--- a/reports/Aperion-Test-Cases.xlsx
+++ b/reports/Aperion-Test-Cases.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="1665">
   <si>
     <t>Aperion Health - Wellness / Advisor Portal - Test Case Document</t>
   </si>
   <si>
-    <t>Generated: 2026-09-03     |     Total Test Cases: 184     |     Automated: 65     |     Manual: 119     |     Pass: 176     |     Fail: 2</t>
+    <t>Generated: 2026-09-17     |     Total Test Cases: 288     |     Automated: 169     |     Manual: 119     |     Pass: 118     |     Fail: 1</t>
   </si>
   <si>
     <t>Manual cases are imported from the team sheet (npm run import). Automated cases are filled in by the Playwright suite - where an automated test reuses a case ID, its run result replaces the manual Status and Actual Result. Status is a dropdown; colours follow the value.</t>
@@ -3240,7 +3240,30 @@
     <t>The dashboard loads without redirecting to /login, the logged-out marketing/OTP screen is not shown, and a non-empty aperion_token is present in localStorage.</t>
   </si>
   <si>
-    <t>As expected.</t>
+    <t>Not Executed</t>
+  </si>
+  <si>
+    <t>TC-TEMPLATE-001</t>
+  </si>
+  <si>
+    <t>Care Plan</t>
+  </si>
+  <si>
+    <t>Member can open and read their active care plan</t>
+  </si>
+  <si>
+    <t>Logged in as a member who has at least one active care plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. From the dashboard, click "Care Plan" in the sidebar.
+2. Select the active plan card.
+3. Read the plan header details.</t>
+  </si>
+  <si>
+    <t>Member: test member account; Plan: any active plan</t>
+  </si>
+  <si>
+    <t>Plan name, start date and assigned coach are all displayed on the plan header.</t>
   </si>
   <si>
     <t>AP_TC_132</t>
@@ -3511,12 +3534,6 @@
     <t>The session is created and listed with a Scheduled status; after cancelling with a reason, the same row shows a Cancelled status and offers to reschedule.</t>
   </si>
   <si>
-    <t>Not run.</t>
-  </si>
-  <si>
-    <t>Skipped</t>
-  </si>
-  <si>
     <t>AP_TC_171</t>
   </si>
   <si>
@@ -3674,76 +3691,87 @@
     <t>No screening conditions are listed and the page shows an empty state instead of the full catalogue.</t>
   </si>
   <si>
-    <t>AP_TC_153</t>
-  </si>
-  <si>
-    <t>Advisor Portal → Messages</t>
-  </si>
-  <si>
-    <t>Verify the Communication Center loads sent communications with column headers</t>
-  </si>
-  <si>
-    <t>Advisor is logged in and at least one communication has been sent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Messages from the sidebar.
-2. Observe the communications list and its column headers.</t>
-  </si>
-  <si>
-    <t>The Communication Center heading is shown with the RECIPIENT, SUBJECT and CHANNEL column headers and at least one communication row.</t>
-  </si>
-  <si>
-    <t>AP_TC_154</t>
-  </si>
-  <si>
-    <t>Verify communications can be filtered by the Email and SMS channels</t>
-  </si>
-  <si>
-    <t>Advisor is on the Communication Center page with communications listed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Note the total number of communications under the "All" filter.
-2. Click the "Email" channel filter and observe the list.
-3. Click the "SMS" channel filter and observe the list.
-4. Click "All" to restore the full list.</t>
-  </si>
-  <si>
-    <t>Channels: All, Email, SMS</t>
-  </si>
-  <si>
-    <t>Each channel filter narrows the list to that channel only, and "All" restores the original number of communications.</t>
-  </si>
-  <si>
-    <t>AP_TC_155</t>
-  </si>
-  <si>
-    <t>Verify the Compose action opens the message composer</t>
-  </si>
-  <si>
-    <t>Advisor is on the Communication Center page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "Compose".
-2. Observe the composer surface.</t>
-  </si>
-  <si>
-    <t>A message composer opens as a dialog or a dedicated view without an application error. No message is sent.</t>
-  </si>
-  <si>
-    <t>AP_TC_156</t>
-  </si>
-  <si>
-    <t>NEGATIVE - Verify searching communications for an unknown recipient returns no results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Type a recipient that does not exist into "Search communications...".
-2. Observe the communications list.</t>
-  </si>
-  <si>
-    <t>Search term: "zzzzz-no-such-recipient"</t>
-  </si>
-  <si>
-    <t>No communication rows are returned and an empty state is displayed.</t>
+    <t>AP_TC_267</t>
+  </si>
+  <si>
+    <t>Verify the gender filter shows sex-specific screenings only for the chosen gender</t>
+  </si>
+  <si>
+    <t>Advisor is on the Navigation Matrix with the full catalogue loaded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Choose "Female" in "Filter by gender".
+2. Observe the condition cards.</t>
+  </si>
+  <si>
+    <t>Gender: Female</t>
+  </si>
+  <si>
+    <t>Breast Cancer and Cervical Cancer cards remain, Prostate Cancer (PSA) is removed, and the card count drops.</t>
+  </si>
+  <si>
+    <t>AP_TC_268</t>
+  </si>
+  <si>
+    <t>Verify the age filter hides screenings that do not apply at that age</t>
+  </si>
+  <si>
+    <t>Advisor is on the Navigation Matrix.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter age 30.
+2. Observe the cards.</t>
+  </si>
+  <si>
+    <t>Age: 30</t>
+  </si>
+  <si>
+    <t>AAA (Aortic Aneurysm), which applies to men 65-75, is no longer listed; age-appropriate screenings remain.</t>
+  </si>
+  <si>
+    <t>AP_TC_269</t>
+  </si>
+  <si>
+    <t>Verify the priority and commonness filters narrow the catalogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Choose a priority in "Filter by priority".
+2. Note the count; Clear all.
+3. Choose a commonness in "Filter by commonness".</t>
+  </si>
+  <si>
+    <t>First non-default option of each filter</t>
+  </si>
+  <si>
+    <t>Each filter reduces the number of cards and Clear all restores the full set.</t>
+  </si>
+  <si>
+    <t>AP_TC_270</t>
+  </si>
+  <si>
+    <t>Verify the matrix can be switched between Grid and List views</t>
+  </si>
+  <si>
+    <t>Advisor is on the Navigation Matrix (Grid).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "List".
+2. Click "Grid".</t>
+  </si>
+  <si>
+    <t>List view renders the conditions as a table; Grid restores the cards.</t>
+  </si>
+  <si>
+    <t>AP_TC_272</t>
+  </si>
+  <si>
+    <t>Verify a condition card shows target population, age-based eligibility and clinical notes</t>
+  </si>
+  <si>
+    <t>1. Read the first condition card.</t>
+  </si>
+  <si>
+    <t>The card shows Target population, Age-based eligibility bands (18–39, 40–49, 50–64, 65+) and Clinical notes, plus the eligibility legend.</t>
   </si>
   <si>
     <t>AP_TC_157</t>
@@ -3752,33 +3780,30 @@
     <t>Advisor Portal → Help &amp; Support</t>
   </si>
   <si>
-    <t>Verify the Help &amp; Support page loads the contact form, knowledge base and live chat</t>
+    <t>Verify the Help &amp; Support page loads contact details, knowledge base, live chat and FAQs</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open Help &amp; Support from the sidebar.
-2. Observe the support options and the contact form fields.</t>
-  </si>
-  <si>
-    <t>The Help &amp; Support heading is shown with the Contact Support, Knowledge Base and Live Chat sections, and the contact form exposes name, email, subject and message fields.</t>
+2. Observe the support sections and the FAQ list.</t>
+  </si>
+  <si>
+    <t>The Help &amp; Support heading is shown with a Contact Support card (phone number, hours, support email), Knowledge Base and Live Chat cards (currently "Coming Soon") and a Frequently Asked Questions list.</t>
   </si>
   <si>
     <t>AP_TC_158</t>
   </si>
   <si>
-    <t>Verify the support contact form pre-fills the logged-in advisor email address</t>
-  </si>
-  <si>
-    <t>Advisor is logged in and on the Help &amp; Support page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate the email field on the Contact Support form.
-2. Read its value.</t>
-  </si>
-  <si>
-    <t>The logged-in advisor account email</t>
-  </si>
-  <si>
-    <t>The email field is pre-populated with the signed-in advisor's email address so it does not have to be retyped.</t>
+    <t>Verify the support email is offered as a mailto link</t>
+  </si>
+  <si>
+    <t>Advisor is on the Help &amp; Support page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Locate the support email in the Contact Support card.
+2. Inspect the link target.</t>
+  </si>
+  <si>
+    <t>The support email address is a "mailto:" link so it opens the advisor's mail client.</t>
   </si>
   <si>
     <t>AP_TC_159</t>
@@ -3787,15 +3812,14 @@
     <t>Verify a knowledge base FAQ entry expands to reveal its answer</t>
   </si>
   <si>
-    <t>Advisor is on the Help &amp; Support page with the Knowledge Base listed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate the FAQ entry "How do I manage my sessions calendar?".
-2. Click the entry.
-3. Observe the answer content.</t>
-  </si>
-  <si>
-    <t>FAQ: "How do I manage my sessions calendar?"</t>
+    <t>Advisor is on the Help &amp; Support page with the FAQ list shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the first FAQ question.
+2. Observe the answer content.</t>
+  </si>
+  <si>
+    <t>FAQ: "How do I schedule advisory sessions with members?"</t>
   </si>
   <si>
     <t>The FAQ entry expands and reveals additional answer text without navigating away from the page.</t>
@@ -3804,22 +3828,56 @@
     <t>AP_TC_160</t>
   </si>
   <si>
-    <t>NEGATIVE - Verify the support request cannot be submitted with an invalid email address</t>
-  </si>
-  <si>
-    <t>Advisor is on the Help &amp; Support page with the Contact Support form displayed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter a name and a subject.
-2. Replace the email address with an invalid value such as "not-an-email".
-3. Enter a message.
-4. Attempt to submit the form.</t>
-  </si>
-  <si>
-    <t>Name: Test Advisor; Email: "not-an-email"; Subject: Automated negative check</t>
-  </si>
-  <si>
-    <t>The form refuses the submission - the submit control stays disabled or a validation message is shown - and no support ticket is created.</t>
+    <t>NEGATIVE - Verify a support request cannot be submitted until category, title and a 20+ character description are provided</t>
+  </si>
+  <si>
+    <t>Advisor is logged in; the header "Support" button is available on every page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Support" in the page header.
+2. Observe the submit control with the form empty.
+3. Pick a category and a title but type a description shorter than 20 characters.
+4. Observe the submit control.</t>
+  </si>
+  <si>
+    <t>Category: Feedback; Title: "Automated negative check"; Description: "too short"</t>
+  </si>
+  <si>
+    <t>"Submit Request" stays disabled while the form is incomplete; no ticket is created.</t>
+  </si>
+  <si>
+    <t>AP_TC_204</t>
+  </si>
+  <si>
+    <t>Verify the header Support modal offers Issue / Feedback / Feature Request categories, title, description and attachments</t>
+  </si>
+  <si>
+    <t>Advisor is logged in.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Support" in the page header.
+2. Observe the modal fields.
+3. Close it with Cancel.</t>
+  </si>
+  <si>
+    <t>A Contact Support modal opens with the three category buttons, a Title (max 200), a Description (minimum 20 characters), an attachments drop zone (JPG/PNG/WebP/MP4/MOV, up to 5 files) and Cancel / Submit Request.</t>
+  </si>
+  <si>
+    <t>AP_TC_205</t>
+  </si>
+  <si>
+    <t>Verify a complete support request can be submitted from the header Support modal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the header Support modal.
+2. Choose Feedback, enter a title and a 20+ character description.
+3. Click "Submit Request".</t>
+  </si>
+  <si>
+    <t>Category: Feedback; Title: "Automated QA ticket"; Description: "Automated test submission from the QA suite - please ignore."</t>
+  </si>
+  <si>
+    <t>"Submit Request" becomes enabled once the form is valid and the modal closes after submission.</t>
   </si>
   <si>
     <t>AP_TC_161</t>
@@ -3872,6 +3930,65 @@
   </si>
   <si>
     <t>The advisor is taken to the Members page and the Members heading is displayed.</t>
+  </si>
+  <si>
+    <t>AP_TC_277</t>
+  </si>
+  <si>
+    <t>Verify changing the reporting period recalculates the metrics</t>
+  </si>
+  <si>
+    <t>Advisor is on the Reports page with the default "Last 7 days" period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Read the Sessions Completed value.
+2. Switch the period to "All time".
+3. Read the value again.</t>
+  </si>
+  <si>
+    <t>Periods: Last 7 days, All time</t>
+  </si>
+  <si>
+    <t>The Sessions Completed value changes (All time is greater than or equal to the 7-day value).</t>
+  </si>
+  <si>
+    <t>AP_TC_278</t>
+  </si>
+  <si>
+    <t>Verify a metric tile drills down to the Sessions page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the "Sessions Completed" tile.
+2. Observe the resulting page.</t>
+  </si>
+  <si>
+    <t>The advisor is taken to /wellness/sessions.</t>
+  </si>
+  <si>
+    <t>AP_TC_279</t>
+  </si>
+  <si>
+    <t>Verify the report charts render (Goal Completion by Member, Sessions By Type, Goals by Category, Session Distribution by Day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Scroll through the report.
+2. Observe each chart section.</t>
+  </si>
+  <si>
+    <t>All four chart sections are present with their titles.</t>
+  </si>
+  <si>
+    <t>AP_TC_280</t>
+  </si>
+  <si>
+    <t>Verify the Reports stats row can be hidden and restored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Hide Stats".
+2. Click "Show Stats".</t>
+  </si>
+  <si>
+    <t>The metric tiles collapse and the control toggles to Show Stats; clicking again restores them.</t>
   </si>
   <si>
     <t>AP_TC_164</t>
@@ -3994,36 +4111,31 @@
     <t>Advisor Portal → Profile</t>
   </si>
   <si>
-    <t>Verify the advisor Profile page loads with its section navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the profile from the avatar menu (or navigate to /wellness/profile).
-2. Observe the profile sections.</t>
-  </si>
-  <si>
-    <t>The Profile heading is shown together with Overview, Personal Information, Address Information, Professional Information, Languages Spoken, About and Expertise &amp; Specialties sections, and a "Back to workspace" control.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test timeout of 30000ms exceeded while running "beforeEach" hook.
-TimeoutError: page.goto: Timeout 30000ms exceeded.
-Call log:
-  - navigating to "https://dev.aperion.health/wellness/profile", waiting until "load"</t>
+    <t>Verify the advisor Profile page loads its overview and all information sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the profile from the avatar (or navigate to /wellness/profile).
+2. Observe the Profile Overview and the information sections.</t>
+  </si>
+  <si>
+    <t>The Profile heading is shown with a Profile Overview (photo, email, experience, languages, Expertise Summary) and the Personal Information, Address Information, Professional Information, Languages Spoken, About and Expertise &amp; Specialties sections, plus a "Back to workspace" control.</t>
   </si>
   <si>
     <t>AP_TC_173</t>
   </si>
   <si>
-    <t>Verify clicking a profile section scrolls to / opens that section</t>
+    <t>Verify "Edit" on Personal Information opens an editable form with the identity fields locked</t>
   </si>
   <si>
     <t>Advisor is on the Profile page.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click the "Personal Information" section control.
-2. Observe the Personal Information section and its Edit control.</t>
-  </si>
-  <si>
-    <t>The Personal Information section is shown (or scrolled into view) with an Edit control, without an application error.</t>
+    <t xml:space="preserve">1. Click "Edit" in the Personal Information section.
+2. Observe the form fields.
+3. Click Cancel.</t>
+  </si>
+  <si>
+    <t>First Name, Last Name, Date of Birth and Gender become editable; Email Address and Phone Number stay disabled; "Save Changes" is disabled until something changes; Cancel restores the read-only view.</t>
   </si>
   <si>
     <t>AP_TC_174</t>
@@ -4037,6 +4149,99 @@
   </si>
   <si>
     <t>The advisor is returned to the workspace (Dashboard), out of /wellness/profile.</t>
+  </si>
+  <si>
+    <t>AP_TC_297</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify a blank First Name is rejected in Personal Information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Edit" in Personal Information.
+2. Clear the First Name field.
+3. Observe the validation and the Save control.</t>
+  </si>
+  <si>
+    <t>First Name: (blank)</t>
+  </si>
+  <si>
+    <t>A "First name is required" message is shown and "Save Changes" stays disabled.</t>
+  </si>
+  <si>
+    <t>AP_TC_298</t>
+  </si>
+  <si>
+    <t>Verify Date of Birth and Gender can be saved and persist after reload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Edit" in Personal Information.
+2. Enter a Date of Birth and pick a Gender.
+3. Click "Save Changes".
+4. Reload the page.</t>
+  </si>
+  <si>
+    <t>DOB: 05/06/1990; Gender: first option</t>
+  </si>
+  <si>
+    <t>An "Information updated" confirmation is shown and the saved values are displayed after reload.</t>
+  </si>
+  <si>
+    <t>AP_TC_299</t>
+  </si>
+  <si>
+    <t>Verify a profile photo (PNG) can be uploaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Choose File" and pick a PNG under 3 MB.
+2. Click "Upload Photo".</t>
+  </si>
+  <si>
+    <t>File: 1x1 PNG</t>
+  </si>
+  <si>
+    <t>"Upload Photo" enables after a file is chosen and the photo is uploaded; the overview shows the image.</t>
+  </si>
+  <si>
+    <t>AP_TC_301</t>
+  </si>
+  <si>
+    <t>Verify Address Information and Languages Spoken have editable forms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Edit" in Address Information; observe the form; Cancel.
+2. Click "Edit" in Languages Spoken; observe; Cancel.</t>
+  </si>
+  <si>
+    <t>Address Information exposes editable Address Line 1/2, City, State, ZIP Code and Country; Languages Spoken opens an editor; both close on Cancel.</t>
+  </si>
+  <si>
+    <t>AP_TC_302</t>
+  </si>
+  <si>
+    <t>Verify Professional Information can be edited and saved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Edit" in Professional Information.
+2. Set Years of Experience.
+3. Click "Save Changes".</t>
+  </si>
+  <si>
+    <t>Years of Experience: 4</t>
+  </si>
+  <si>
+    <t>The value is saved and shown in the read-only view.</t>
+  </si>
+  <si>
+    <t>AP_TC_303</t>
+  </si>
+  <si>
+    <t>Verify the Expertise Summary lists the matching dimensions used by the Navigation Matrix</t>
+  </si>
+  <si>
+    <t>1. Locate the Expertise Summary in the Profile Overview.</t>
+  </si>
+  <si>
+    <t>Location Expertise, Health Conditions, Cultural Expertise and Age Groups are listed.</t>
   </si>
   <si>
     <t>AP_TC_175</t>
@@ -4380,6 +4585,1556 @@
     <t>The Annual Road Map screen loads at /wellness/sessions/:id/annual-road-map-review with its Health Profile Comparison section, without an application error.</t>
   </si>
   <si>
+    <t>AP_TC_196</t>
+  </si>
+  <si>
+    <t>Advisor Portal → Authentication &amp; Shell</t>
+  </si>
+  <si>
+    <t>Verify an advisor can log in with email + one-time passcode and reach the portal</t>
+  </si>
+  <si>
+    <t>LOGIN_EMAIL / LOGIN_OTP are set for this environment; the account is an advisor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open /login and choose the Email tab.
+2. Enter the email and click "Send One-Time Passcode".
+3. Enter the 6-digit code on /verify.
+4. Observe where the app lands.</t>
+  </si>
+  <si>
+    <t>Email: LOGIN_EMAIL; OTP: LOGIN_OTP</t>
+  </si>
+  <si>
+    <t>The code is accepted and the app lands on the portal selection page (or directly on the dashboard for single-portal accounts) with a session token stored.</t>
+  </si>
+  <si>
+    <t>AP_TC_197</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify a wrong one-time passcode is rejected</t>
+  </si>
+  <si>
+    <t>LOGIN_EMAIL is set; the account is registered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Request a passcode for the email.
+2. Enter 000000 on /verify.</t>
+  </si>
+  <si>
+    <t>OTP: 000000</t>
+  </si>
+  <si>
+    <t>"Invalid OTP code. Please try again." is shown, the user stays on /verify and a Resend OTP countdown is offered.</t>
+  </si>
+  <si>
+    <t>AP_TC_198</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify an unregistered email cannot request a passcode</t>
+  </si>
+  <si>
+    <t>User is on /login.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Choose the Email tab.
+2. Enter an unregistered address and click "Send One-Time Passcode".</t>
+  </si>
+  <si>
+    <t>Email: zzzzz-not-registered-9999@example.com</t>
+  </si>
+  <si>
+    <t>An "Account not found" message is shown and the user stays on /login.</t>
+  </si>
+  <si>
+    <t>AP_TC_199</t>
+  </si>
+  <si>
+    <t>Verify the Phone tab requests a passcode by SMS</t>
+  </si>
+  <si>
+    <t>LOGIN_PHONE is set to a registered US number (digits only).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open /login (Phone tab is default).
+2. Enter the number and click "Send One-Time Passcode".</t>
+  </si>
+  <si>
+    <t>Phone: LOGIN_PHONE</t>
+  </si>
+  <si>
+    <t>The app moves to /verify and says the code was sent to the phone.</t>
+  </si>
+  <si>
+    <t>AP_TC_206</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify a member account cannot reach Advisor Portal routes</t>
+  </si>
+  <si>
+    <t>MEMBER_LOGIN_EMAIL / LOGIN_OTP are set for a member (non-advisor) account.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in as the member.
+2. Navigate to /wellness/dashboard.
+3. Navigate to /wellness/admin/overview.</t>
+  </si>
+  <si>
+    <t>Email: MEMBER_LOGIN_EMAIL</t>
+  </si>
+  <si>
+    <t>The member lands on /member/dashboard and every /wellness/* route redirects back to the member dashboard.</t>
+  </si>
+  <si>
+    <t>AP_TC_200</t>
+  </si>
+  <si>
+    <t>Verify the portal selection page lists the portals and opens the Advisor Portal</t>
+  </si>
+  <si>
+    <t>Advisor is logged in with access to more than one portal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open /auth/portal-selection.
+2. Observe the portal cards.
+3. Click Advisor Portal.</t>
+  </si>
+  <si>
+    <t>"Select Your Portal" lists the account's portals (Advisor Portal included) and choosing Advisor Portal opens /wellness/dashboard.</t>
+  </si>
+  <si>
+    <t>AP_TC_201</t>
+  </si>
+  <si>
+    <t>Verify "Switch Portal" returns to the portal picker</t>
+  </si>
+  <si>
+    <t>Advisor is on any Advisor Portal page.</t>
+  </si>
+  <si>
+    <t>1. Click "Switch Portal" in the sidebar.</t>
+  </si>
+  <si>
+    <t>The portal selection page opens.</t>
+  </si>
+  <si>
+    <t>AP_TC_203</t>
+  </si>
+  <si>
+    <t>Verify every sidebar entry opens its page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click each Workspace and Administration entry in turn.
+2. Observe the page heading.</t>
+  </si>
+  <si>
+    <t>Dashboard, Members, Sessions, Care Scheduler, Navigation Matrix, Communication Center, Help &amp; Support, Reports, Admin</t>
+  </si>
+  <si>
+    <t>Each entry navigates to its page and the matching heading is shown.</t>
+  </si>
+  <si>
+    <t>AP_TC_207</t>
+  </si>
+  <si>
+    <t>Verify the sidebar can be collapsed and expanded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Collapse sidebar".
+2. Click "Expand sidebar".</t>
+  </si>
+  <si>
+    <t>The sidebar collapses to icons and the control toggles; expanding restores the labels.</t>
+  </si>
+  <si>
+    <t>AP_TC_216</t>
+  </si>
+  <si>
+    <t>Advisor Portal → Members → Member Profile</t>
+  </si>
+  <si>
+    <t>Verify the member profile header and section navigation</t>
+  </si>
+  <si>
+    <t>Advisor is logged in; the member is on the advisor's caseload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Members, search the member and click View.
+2. Observe the header and the left navigation.</t>
+  </si>
+  <si>
+    <t>Member: Anthony Stark</t>
+  </si>
+  <si>
+    <t>The header shows the member name, status, Back to Members, Schedule session and Message; the navigation lists Chart, Journey, Wellness Profile, Care Plans, Health Plan, Dependents, Sessions, Documents, Chat History, Call History and Advisor History.</t>
+  </si>
+  <si>
+    <t>AP_TC_217</t>
+  </si>
+  <si>
+    <t>Verify the Chart section shows Personal Information, dependents count and last visit</t>
+  </si>
+  <si>
+    <t>Advisor is on the member profile.</t>
+  </si>
+  <si>
+    <t>1. Observe the Chart section.</t>
+  </si>
+  <si>
+    <t>Personal Information (name, email, phone, DOB, gender, employer, member since, address) plus Dependents and Last visit summaries are shown.</t>
+  </si>
+  <si>
+    <t>AP_TC_218</t>
+  </si>
+  <si>
+    <t>Verify the Journey section switches between Classic and Enhanced views</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Journey.
+2. Click "Enhanced".
+3. Click "Classic".</t>
+  </si>
+  <si>
+    <t>Both views render (timeline or "Nothing completed yet" empty state) with the toggle reflecting the selection.</t>
+  </si>
+  <si>
+    <t>AP_TC_219</t>
+  </si>
+  <si>
+    <t>Verify the Care Plans section loads (plans or empty state)</t>
+  </si>
+  <si>
+    <t>1. Open Care Plans.</t>
+  </si>
+  <si>
+    <t>The section renders either the member's treatment plans or "No care plans", without an error.</t>
+  </si>
+  <si>
+    <t>AP_TC_220</t>
+  </si>
+  <si>
+    <t>Verify the Health Plan section shows the member's insurance plan details</t>
+  </si>
+  <si>
+    <t>Advisor is on the member profile of a member with a health plan.</t>
+  </si>
+  <si>
+    <t>1. Open Health Plan.</t>
+  </si>
+  <si>
+    <t>Plan name, carrier, status, Member ID, Group number, Plan code, Network, Coverage tier and Effective date are shown.</t>
+  </si>
+  <si>
+    <t>AP_TC_221</t>
+  </si>
+  <si>
+    <t>Verify the Dependents section lists each dependent with relationship, date of birth and gender</t>
+  </si>
+  <si>
+    <t>Advisor is on the member profile of a member with dependents.</t>
+  </si>
+  <si>
+    <t>1. Open Dependents.</t>
+  </si>
+  <si>
+    <t>Each dependent row shows a name, relationship (e.g. Parent / Child), DOB and gender.</t>
+  </si>
+  <si>
+    <t>AP_TC_222</t>
+  </si>
+  <si>
+    <t>Verify the Sessions section shows the five advisory sessions in order plus the Care Scheduler table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Sessions.
+2. Observe the Advisory Sessions table and the Care Scheduler table.</t>
+  </si>
+  <si>
+    <t>Advisory Sessions lists Health Assessment, Pre Visit Session, Post-Visit Session, Wellness Check-in and Annual Road Map (in that order) with sortable Session / Scheduled / Status columns and per-row actions; the Care Scheduler table lists appointments with Mark complete actions.</t>
+  </si>
+  <si>
+    <t>AP_TC_223</t>
+  </si>
+  <si>
+    <t>Verify "Schedule" on an unscheduled session type opens the booking dialog with the member pre-selected</t>
+  </si>
+  <si>
+    <t>Advisor is on the member's Sessions section with at least one "Not Scheduled" session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Schedule" on a Not Scheduled row.
+2. Observe the dialog.
+3. Close it.</t>
+  </si>
+  <si>
+    <t>The "Book a session" dialog opens with Member already set to this member.</t>
+  </si>
+  <si>
+    <t>AP_TC_224</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify "Skip" on a session requires a reason before it can be confirmed</t>
+  </si>
+  <si>
+    <t>Advisor is on the member's Sessions section with a skippable session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Skip" on a Not Scheduled row.
+2. Observe the Skip Session modal with the Reason blank.
+3. Click "Keep Session".</t>
+  </si>
+  <si>
+    <t>Reason: (blank)</t>
+  </si>
+  <si>
+    <t>The Skip Session modal explains a note is required; "Skip Session" is disabled until a reason is typed; Keep Session closes it without changes.</t>
+  </si>
+  <si>
+    <t>AP_TC_225</t>
+  </si>
+  <si>
+    <t>Verify "Reschedule" on an overdue session opens the Edit session panel with the member locked</t>
+  </si>
+  <si>
+    <t>Advisor is on the member's Sessions section with an Overdue session.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Reschedule" on an Overdue row.
+2. Observe the Edit session panel.
+3. Cancel.</t>
+  </si>
+  <si>
+    <t>An "Edit session" panel opens with Member disabled, the session type pre-filled, a date picker, times, meeting type and Save changes.</t>
+  </si>
+  <si>
+    <t>AP_TC_226</t>
+  </si>
+  <si>
+    <t>Verify the advisor can upload a document to the member's Documents</t>
+  </si>
+  <si>
+    <t>Advisor is on the member's Documents section.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Upload".
+2. Choose a PNG and a category.
+3. Confirm the upload.</t>
+  </si>
+  <si>
+    <t>The document count increases and the new file is listed as uploaded by the advisor.</t>
+  </si>
+  <si>
+    <t>AP_TC_227</t>
+  </si>
+  <si>
+    <t>Verify a document can be previewed from the Documents section</t>
+  </si>
+  <si>
+    <t>Advisor is on the member's Documents section with at least one document.</t>
+  </si>
+  <si>
+    <t>1. Click "Preview" on a document.</t>
+  </si>
+  <si>
+    <t>A preview opens (dialog or viewer) without an application error.</t>
+  </si>
+  <si>
+    <t>AP_TC_228</t>
+  </si>
+  <si>
+    <t>Verify Chat History lists on-demand conversations and opens a transcript</t>
+  </si>
+  <si>
+    <t>Advisor is on the profile of a member with chat history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Chat History.
+2. Click a conversation entry.</t>
+  </si>
+  <si>
+    <t>Conversations are listed with date, status and duration; clicking one shows its transcript.</t>
+  </si>
+  <si>
+    <t>AP_TC_229</t>
+  </si>
+  <si>
+    <t>Verify Call History loads (calls or "No call history" empty state)</t>
+  </si>
+  <si>
+    <t>1. Open Call History.</t>
+  </si>
+  <si>
+    <t>The Call History heading is shown with either call entries or the "No call history" empty state.</t>
+  </si>
+  <si>
+    <t>AP_TC_230</t>
+  </si>
+  <si>
+    <t>Verify Advisor History shows the current advisor and previous assignments</t>
+  </si>
+  <si>
+    <t>1. Open Advisor History.</t>
+  </si>
+  <si>
+    <t>The current advisor is marked "Current" with the assignment period; previous advisors (if any) list their period and reason.</t>
+  </si>
+  <si>
+    <t>AP_TC_231</t>
+  </si>
+  <si>
+    <t>Verify the session status filter lists all statuses and filters the list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the "All Statuses" dropdown.
+2. Observe the options.
+3. Choose "Completed".</t>
+  </si>
+  <si>
+    <t>Statuses: Scheduled, In Progress, Completed, Cancelled, Skipped</t>
+  </si>
+  <si>
+    <t>All five statuses are offered and the list re-renders without an application error.</t>
+  </si>
+  <si>
+    <t>AP_TC_232</t>
+  </si>
+  <si>
+    <t>Verify the session type filter lists the five session types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the "All Session Types" dropdown.
+2. Observe the options.
+3. Choose "Health Assessment".</t>
+  </si>
+  <si>
+    <t>Types: Health Assessment, Pre Visit Session, Post-Visit Session, Wellness Check-in, Annual Road Map</t>
+  </si>
+  <si>
+    <t>All five types are offered and the list re-renders without an application error.</t>
+  </si>
+  <si>
+    <t>AP_TC_233</t>
+  </si>
+  <si>
+    <t>Verify the calendar Previous / Next / Today controls move the displayed month</t>
+  </si>
+  <si>
+    <t>Advisor is on the Sessions page in Month view.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Switch to Month view and note the month label.
+2. Click Previous.
+3. Click Next twice.
+4. Click Today.</t>
+  </si>
+  <si>
+    <t>Previous shows the prior month, Next moves forward, and Today returns to the current month.</t>
+  </si>
+  <si>
+    <t>AP_TC_234</t>
+  </si>
+  <si>
+    <t>Verify selecting a day in Month view lists that day's sessions with counts</t>
+  </si>
+  <si>
+    <t>Advisor is on the Sessions page; at least one past day has sessions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Switch to Month view.
+2. Click a day whose button shows "— N sessions".
+3. Observe the Selected Day panel and the list.</t>
+  </si>
+  <si>
+    <t>Any day with sessions in the current or previous month</t>
+  </si>
+  <si>
+    <t>The Selected Day panel shows that date with Sessions / Virtual / Phone counts and the list shows rows for it.</t>
+  </si>
+  <si>
+    <t>AP_TC_235</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify past dates and Sundays cannot be chosen in the booking calendar</t>
+  </si>
+  <si>
+    <t>Advisor has the "Book a session" dialog open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Schedule Session".
+2. Inspect the date buttons for days before today and for Sundays.</t>
+  </si>
+  <si>
+    <t>Current month</t>
+  </si>
+  <si>
+    <t>Days before today are disabled; Sundays are disabled and labelled "Sunday, unavailable"; today is pre-selected.</t>
+  </si>
+  <si>
+    <t>AP_TC_236</t>
+  </si>
+  <si>
+    <t>Verify the booking form auto-fills the title and computes a 45-minute duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Choose a member and a session type.
+2. Observe the Session title and Duration.
+3. Observe the "Still needed" status as fields are filled.</t>
+  </si>
+  <si>
+    <t>Member: first test member; Type: Health Assessment</t>
+  </si>
+  <si>
+    <t>The title becomes "&lt;Member&gt; – &lt;Type&gt;", Duration reads "45 minutes" (auto), and the status text lists only the remaining required fields.</t>
+  </si>
+  <si>
+    <t>AP_TC_237</t>
+  </si>
+  <si>
+    <t>Verify "Generate Zoom link" creates a meeting link for a Virtual session</t>
+  </si>
+  <si>
+    <t>Advisor has the "Book a session" dialog open with a member and type chosen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Keep Meeting type = Virtual.
+2. Click "Generate Zoom link".
+3. Observe the Meeting link field and the Copy control.</t>
+  </si>
+  <si>
+    <t>Meeting type: Virtual</t>
+  </si>
+  <si>
+    <t>A zoom.us join URL is filled in, Copy becomes enabled and the "Still needed" status no longer lists the meeting link. No session is created.</t>
+  </si>
+  <si>
+    <t>AP_TC_238</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify a member cannot be booked for the same session type twice on one day</t>
+  </si>
+  <si>
+    <t>A test member already has a session of some type today (created by this test if needed).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a Phone session for a member.
+2. Open "Book a session" again for the same member.
+3. Open the Session type list.</t>
+  </si>
+  <si>
+    <t>Type: first free type for the member</t>
+  </si>
+  <si>
+    <t>The type just booked is disabled in the list for that member (or the app rejects the duplicate with a "Could not schedule" message).</t>
+  </si>
+  <si>
+    <t>AP_TC_245</t>
+  </si>
+  <si>
+    <t>Verify the session list paginates (rows per page + page controls)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select a day with sessions (or today).
+2. Observe the pagination footer.</t>
+  </si>
+  <si>
+    <t>A "Rows per page" selector and "Showing x–y of n sessions" text with Previous/Next page controls are shown.</t>
+  </si>
+  <si>
+    <t>AP_TC_239</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify a session cannot be cancelled without a reason</t>
+  </si>
+  <si>
+    <t>A Scheduled test session exists (created by this test).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a Phone session.
+2. Click Cancel on its row.
+3. Leave Reason blank and observe "Cancel Session".
+4. Enter a reason and confirm.</t>
+  </si>
+  <si>
+    <t>Reason: (blank) then "AP_TC_239 cleanup"</t>
+  </si>
+  <si>
+    <t>Reason is marked required and "Cancel Session" is disabled while it is blank; with a reason the session is cancelled.</t>
+  </si>
+  <si>
+    <t>AP_TC_240</t>
+  </si>
+  <si>
+    <t>Verify a cancelled session can be rescheduled to another day</t>
+  </si>
+  <si>
+    <t>A Cancelled test session exists (created by this test).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a Phone session and cancel it with a reason.
+2. Click "Reschedule" on the Cancelled row.
+3. In "Edit session" pick the next available day.
+4. Click "Save changes".</t>
+  </si>
+  <si>
+    <t>Type: Wellness Check-in; new date: next enabled day</t>
+  </si>
+  <si>
+    <t>"Edit session" opens with the member locked and the session type pre-filled; after saving, the session is listed as "Rescheduled" on the new day.</t>
+  </si>
+  <si>
+    <t>AP_TC_241</t>
+  </si>
+  <si>
+    <t>Verify Start moves a session to "Waiting for member" and "Member Joined" moves it to In progress</t>
+  </si>
+  <si>
+    <t>A Scheduled test session exists (created by this test). Started sessions cannot be cancelled - this leaves one in-progress session behind.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Book a Phone session.
+2. Click "Start" on the row and confirm "Start session".
+3. Observe the row status and pipeline.
+4. Click "Member Joined".</t>
+  </si>
+  <si>
+    <t>Type: Post-Visit Session</t>
+  </si>
+  <si>
+    <t>The row shows "Waiting for member" with Member Joined / Assessment actions; Member Joined opens the assessment and the status becomes In progress.</t>
+  </si>
+  <si>
+    <t>AP_TC_242</t>
+  </si>
+  <si>
+    <t>Verify "End Meeting" moves an in-progress session to "Wrapping up" and the header shows the active-session banner</t>
+  </si>
+  <si>
+    <t>An in-progress test session exists (AP_TC_241 or created here).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the in-progress session's Assessment.
+2. Observe the header banner.
+3. Click "End Meeting".
+4. Return to Sessions and observe the row.</t>
+  </si>
+  <si>
+    <t>The header shows an "IN PROGRESS … Go to session" banner; End Meeting sets the row to "Wrapping up" with the Assessment action still available.</t>
+  </si>
+  <si>
+    <t>AP_TC_244</t>
+  </si>
+  <si>
+    <t>Verify a completed session offers Assessment and Share, and Share marks the summary as sent</t>
+  </si>
+  <si>
+    <t>A Completed session exists for the advisor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Filter the list to Completed (or pick a past day).
+2. Observe the row actions.
+3. Click "Share".</t>
+  </si>
+  <si>
+    <t>Any completed session</t>
+  </si>
+  <si>
+    <t>The row shows Assessment and Share; after Share the pipeline shows "Summary Sent" / the summary is recorded as shared.</t>
+  </si>
+  <si>
+    <t>AP_TC_246</t>
+  </si>
+  <si>
+    <t>Verify the Health Assessment workflow can be completed end to end (6 steps)</t>
+  </si>
+  <si>
+    <t>Advisor is logged in; a test member has no session of this type today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule a Health Assessment (Phone) for a test member and start it; click Member Joined.
+2. Step 1 Demographics &amp; Physical: enter height/weight (BMI is validated) and Confirm &amp; continue.
+3. Steps 2-5: Employment &amp; Literacy, Lifestyle Habits, Dietary &amp; Behavioral Health, Health Assessment - fill and Confirm &amp; continue.
+4. Step 6 Assessment Review: click "Complete assessment".
+5. Confirm the session shows as Completed in the list.</t>
+  </si>
+  <si>
+    <t>Session type: Health Assessment; realistic values for every required field</t>
+  </si>
+  <si>
+    <t>Every step saves and advances (Demographics &amp; Physical → Employment &amp; Literacy → Lifestyle Habits → Dietary &amp; Behavioral Health → Health Assessment → Assessment Review), the completion button closes the workflow and the session row shows Completed with Assessment and Share actions.</t>
+  </si>
+  <si>
+    <t>AP_TC_250</t>
+  </si>
+  <si>
+    <t>Verify the Post-Visit Session workflow can be completed end to end (5 steps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule a Post-Visit Session (Phone) for a test member and start it; click Member Joined.
+2. Step 1 Screening Planning &amp; Notes: record each screening and Save &amp; Continue.
+3. Step 2 Health Risk Assessment Outcomes: record outcomes and Save &amp; Continue.
+4. Step 3 Doctor Questions - Outcomes and Step 4 Visit Priorities - Achievement Status: Save &amp; Continue.
+5. Step 5 Visit Summary: click "Complete Session".
+6. Confirm the session shows as Completed in the list.</t>
+  </si>
+  <si>
+    <t>Session type: Post-Visit Session; realistic values for every required field</t>
+  </si>
+  <si>
+    <t>Every step saves and advances (Screening Planning &amp; Notes → Health Risk Assessment Outcomes → Doctor Questions - Outcomes → Visit Priorities - Achievement Status → Visit Summary), the completion button closes the workflow and the session row shows Completed with Assessment and Share actions.</t>
+  </si>
+  <si>
+    <t>AP_TC_251</t>
+  </si>
+  <si>
+    <t>Verify the Wellness Check-in workflow can be completed end to end (4 steps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule a Wellness Check-in (Phone) for a test member and start it; click Member Joined.
+2. Step 1 Wellness Progress &amp; Feedback, Step 2 Barriers &amp; Challenges, Step 3 Next Steps &amp; Actions: fill and Save &amp; Continue.
+3. Step 4 Session Summary: click "Complete Session".
+4. Confirm the session shows as Completed in the list.</t>
+  </si>
+  <si>
+    <t>Session type: Wellness Check-in; realistic values for every required field</t>
+  </si>
+  <si>
+    <t>Every step saves and advances (Wellness Progress &amp; Feedback → Barriers &amp; Challenges → Next Steps &amp; Actions → Session Summary), the completion button closes the workflow and the session row shows Completed with Assessment and Share actions.</t>
+  </si>
+  <si>
+    <t>AP_TC_252</t>
+  </si>
+  <si>
+    <t>Verify the Annual Road Map workflow can be completed end to end (5 steps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule a Annual Road Map (Phone) for a test member and start it; click Member Joined.
+2. Step 1 Health Profile Comparison: enter current metrics and Save &amp; Continue.
+3. Step 2 Preventive Care Completion and Step 3 Wellness Goal Achievement: Save &amp; Continue.
+4. Step 4 Member Feedback &amp; Experience: rate each 1-10 scale and Save &amp; Continue.
+5. Step 5 Summary: click "Complete Session".
+6. Confirm the session shows as Completed in the list.</t>
+  </si>
+  <si>
+    <t>Session type: Annual Road Map; realistic values for every required field</t>
+  </si>
+  <si>
+    <t>Every step saves and advances (Health Profile Comparison → Preventive Care Completion → Wellness Goal Achievement → Member Feedback &amp; Experience → Summary), the completion button closes the workflow and the session row shows Completed with Assessment and Share actions.</t>
+  </si>
+  <si>
+    <t>AP_TC_248</t>
+  </si>
+  <si>
+    <t>Verify Pre Visit Session step 1 (Screening Planning) saves and step 2 (Health Risk Assessment) requires every risk item to be recorded</t>
+  </si>
+  <si>
+    <t>Advisor is logged in; a test member has no Pre Visit Session today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule and start a Pre Visit Session; click Member Joined.
+2. Step 1: observe Critical / Advised / Optional groups and the screening cards; click Confirm &amp; continue.
+3. Step 2: observe the four risk categories with three items each; open an item.
+4. Observe "Confirm &amp; continue" before all items are recorded.</t>
+  </si>
+  <si>
+    <t>Session type: Pre Visit Session</t>
+  </si>
+  <si>
+    <t>Step 1 saves (screening step marked reviewed) and step 2 lists Cardiovascular Health, Metabolic &amp; Diabetes Risk, Men's/Women's Health Concerns and Mental Health &amp; Wellbeing; each item needs a Risk level and Notes; "Confirm &amp; continue" stays disabled until every item is saved, skipped or removed.</t>
+  </si>
+  <si>
+    <t>AP_TC_247</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify the Health Assessment rejects implausible physical measurements (BMI check)</t>
+  </si>
+  <si>
+    <t>An in-progress Health Assessment is open (created by this test).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule and start a Health Assessment; click Member Joined.
+2. Enter height 6 ft 6 in and weight 60 lbs.
+3. Click "Confirm &amp; continue".</t>
+  </si>
+  <si>
+    <t>Height: 6'6"; Weight: 60 lbs (BMI ≈ 6.9)</t>
+  </si>
+  <si>
+    <t>A BMI warning ("extremely low… verify the values") is shown and the step does not advance.</t>
+  </si>
+  <si>
+    <t>AP_TC_253</t>
+  </si>
+  <si>
+    <t>Verify an in-progress workflow retains saved data when reopened</t>
+  </si>
+  <si>
+    <t>An in-progress Health Assessment with step 1 saved exists (created by this test).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule and start a Health Assessment; click Member Joined.
+2. Enter 5 ft 8 in / 170 lbs and Confirm &amp; continue.
+3. Return to Sessions and open the Assessment again.
+4. Observe step 1 values.</t>
+  </si>
+  <si>
+    <t>Height 5'8", Weight 170 lbs</t>
+  </si>
+  <si>
+    <t>The saved measurements are shown again (the workflow reopens on step 1 - progress position is not remembered, data is).</t>
+  </si>
+  <si>
+    <t>AP_TC_254</t>
+  </si>
+  <si>
+    <t>Verify workflow journey steps are gated sequentially and the Member info panel collapses</t>
+  </si>
+  <si>
+    <t>An in-progress Post-Visit Session is open (created by this test).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Schedule and start a Post-Visit Session; click Member Joined.
+2. Observe the Journey progress steps.
+3. Click "Collapse Member info".</t>
+  </si>
+  <si>
+    <t>Steps 02-05 are disabled until step 01 is saved; History and End Meeting are available; the Member info panel collapses.</t>
+  </si>
+  <si>
+    <t>AP_TC_256</t>
+  </si>
+  <si>
+    <t>Verify the Care Scheduler stat tiles (Total requests, In progress, Closed) are shown</t>
+  </si>
+  <si>
+    <t>Advisor is on the Care Scheduler page.</t>
+  </si>
+  <si>
+    <t>1. Observe the tiles above the request list.</t>
+  </si>
+  <si>
+    <t>Total requests, In progress and Closed tiles are shown with counts.</t>
+  </si>
+  <si>
+    <t>AP_TC_257</t>
+  </si>
+  <si>
+    <t>Verify the request status filter offers every request status and narrows the list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open "Filter by status".
+2. Observe the options.
+3. Choose "Completed".</t>
+  </si>
+  <si>
+    <t>Statuses: Pending, In Progress, Completed, Unreported, Cancelled</t>
+  </si>
+  <si>
+    <t>The status options are listed (each once) and applying one leaves only rows with that status.</t>
+  </si>
+  <si>
+    <t>AP_TC_258</t>
+  </si>
+  <si>
+    <t>Verify the employer filter narrows the request list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Filter by employer…" and pick an employer.
+2. Observe the list.
+3. Click "Clear all".</t>
+  </si>
+  <si>
+    <t>First employer in the list</t>
+  </si>
+  <si>
+    <t>Only that employer's requests remain; Clear all restores the full list.</t>
+  </si>
+  <si>
+    <t>AP_TC_259</t>
+  </si>
+  <si>
+    <t>Verify the request list can be sorted by Submitted date</t>
+  </si>
+  <si>
+    <t>Advisor is on the Care Scheduler page with at least two requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Sort by Submitted" twice.
+2. Compare the first row each time.</t>
+  </si>
+  <si>
+    <t>The order of the rows changes between ascending and descending.</t>
+  </si>
+  <si>
+    <t>AP_TC_260</t>
+  </si>
+  <si>
+    <t>Verify request list pagination (rows per page and page controls)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Observe the pagination footer.
+2. Open "Rows per page".</t>
+  </si>
+  <si>
+    <t>"Showing x–y of n requests", Previous/Next page controls and a Rows per page selector are shown.</t>
+  </si>
+  <si>
+    <t>AP_TC_261</t>
+  </si>
+  <si>
+    <t>Verify searching by Request ID finds the request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Read a Request ID from the list.
+2. Type it into the search box.</t>
+  </si>
+  <si>
+    <t>First listed REQ-… id</t>
+  </si>
+  <si>
+    <t>Exactly that request remains listed.</t>
+  </si>
+  <si>
+    <t>AP_TC_262</t>
+  </si>
+  <si>
+    <t>Verify the request details page shows the member panel, request facts, slot preferences and an advisor note</t>
+  </si>
+  <si>
+    <t>Advisor is on the Care Scheduler page with at least one request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "View Details" on a request.
+2. Observe the page.</t>
+  </si>
+  <si>
+    <t>First listed request</t>
+  </si>
+  <si>
+    <t>A details page (/care-scheduler/requests/:id) shows the member's contact and location (read-only), Request ID, appointment type, preferred provider, submitted date, Primary/Secondary slot preferences and an Advisor note field, plus "Back to Requests".</t>
+  </si>
+  <si>
+    <t>AP_TC_263</t>
+  </si>
+  <si>
+    <t>Verify the review checklist gates "Mark as Reviewed" until every item is confirmed</t>
+  </si>
+  <si>
+    <t>A Pending request exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a Pending request.
+2. Observe "Mark as Reviewed" with nothing checked.
+3. Click "Select All".
+4. Observe the control.</t>
+  </si>
+  <si>
+    <t>First Pending request</t>
+  </si>
+  <si>
+    <t>"Mark as Reviewed" is disabled until Member need, Contact details, Location and Preferred times are all confirmed; Select All enables it.</t>
+  </si>
+  <si>
+    <t>AP_TC_264</t>
+  </si>
+  <si>
+    <t>Verify "Mark as Reviewed" moves a Pending request to In Progress and opens the provider-call step</t>
+  </si>
+  <si>
+    <t>A Pending request exists (this test changes its status).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a Pending request.
+2. Click "Select All" then "Mark as Reviewed".
+3. Observe the next step and the queue status.</t>
+  </si>
+  <si>
+    <t>The page advances to "Call the provider &amp; check availability" with per-slot Confirmed / Not Available controls, and the queue shows the request as In Progress.</t>
+  </si>
+  <si>
+    <t>AP_TC_265</t>
+  </si>
+  <si>
+    <t>Verify the provider-call step records slot outcomes and gates Continue until a slot is confirmed</t>
+  </si>
+  <si>
+    <t>An In Progress request exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Filter to In Progress and open a request.
+2. Observe the provider card and slot controls.
+3. Observe "Continue".</t>
+  </si>
+  <si>
+    <t>First In Progress request</t>
+  </si>
+  <si>
+    <t>The provider name/phone/address are shown; each preferred slot has Confirmed / Not Available; "Still needed: a slot the provider can confirm" is shown and Continue is disabled until then; Close request is available.</t>
+  </si>
+  <si>
+    <t>AP_TC_266</t>
+  </si>
+  <si>
+    <t>Verify the Confirmed Appointments view shows the upcoming count and the list or empty state</t>
+  </si>
+  <si>
+    <t>1. Open /wellness/care-scheduler/confirmed.</t>
+  </si>
+  <si>
+    <t>"Upcoming Appointments (n)" is shown with either appointment rows or "No Confirmed Appointments".</t>
+  </si>
+  <si>
+    <t>AP_TC_281</t>
+  </si>
+  <si>
+    <t>Verify the advisor roster filters (specialty, capacity, status), positive search and Grid view</t>
+  </si>
+  <si>
+    <t>Advisor has administration access; advisors exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open each filter and observe its options.
+2. Search for an existing advisor by name.
+3. Apply a status filter.
+4. Switch to Grid.</t>
+  </si>
+  <si>
+    <t>Search: the first listed advisor's name</t>
+  </si>
+  <si>
+    <t>Specialty, capacity (No members / Carrying members) and status (Active / Pending / On leave / Paused / Departed) filters are offered; the search narrows to the advisor; Grid renders cards with View actions.</t>
+  </si>
+  <si>
+    <t>AP_TC_282</t>
+  </si>
+  <si>
+    <t>Verify the Profile tab shows the advisor's details</t>
+  </si>
+  <si>
+    <t>Advisor has administration access and opened an advisor.</t>
+  </si>
+  <si>
+    <t>1. Observe the Profile tab (default).</t>
+  </si>
+  <si>
+    <t>First listed advisor</t>
+  </si>
+  <si>
+    <t>The advisor's name heading, contact details and section links (Profile, Assigned members, Workload, Lifecycle) are shown.</t>
+  </si>
+  <si>
+    <t>AP_TC_283</t>
+  </si>
+  <si>
+    <t>Verify the Caseload tab lists assigned members and offers the "Assign members" wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Assigned members".
+2. Observe the table and the "Assign members" action.
+3. Click "Assign members"; observe; Cancel.</t>
+  </si>
+  <si>
+    <t>The caseload table (Member, Employer, Location, Progress) and search/List/Grid controls are shown; "Assign members" opens a wizard whose destination is this advisor ("Pick members from the unassigned pool").</t>
+  </si>
+  <si>
+    <t>AP_TC_284</t>
+  </si>
+  <si>
+    <t>Verify "Set availability" on the Lifecycle tab offers On leave / Paused (cancelled without saving)</t>
+  </si>
+  <si>
+    <t>Advisor is on an advisor's Lifecycle tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Lifecycle".
+2. Click "Set availability".
+3. Observe the options.
+4. Cancel.</t>
+  </si>
+  <si>
+    <t>A "Set availability" dialog explains the current status and offers On leave and Paused; Cancel closes it without changing the status.</t>
+  </si>
+  <si>
+    <t>AP_TC_285</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify "Off board" requires a reason before a departure can be started (cancelled without saving)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Off board".
+2. Observe the dialog with no reason chosen.
+3. Cancel.</t>
+  </si>
+  <si>
+    <t>An "Off-board &lt;advisor&gt;?" dialog explains that members must be handed over; the primary action stays disabled until a reason is chosen; Cancel closes it and no departure is created.</t>
+  </si>
+  <si>
+    <t>AP_TC_286</t>
+  </si>
+  <si>
+    <t>Verify Admin → Members shows assignment stats and the Pending / Assigned tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Observe the stat tiles.
+2. Click the "Assigned" tab.
+3. Click the "Pending" tab.</t>
+  </si>
+  <si>
+    <t>Total Members, Pending Assignment, Assigned and Longest Wait tiles are shown; the Pending tab lists unassigned members with an Assign action and the Assigned tab lists members with their advisor.</t>
+  </si>
+  <si>
+    <t>AP_TC_287</t>
+  </si>
+  <si>
+    <t>Verify the employer, risk and account-status filters on Admin → Members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open each filter and observe its options.
+2. Apply a risk filter.</t>
+  </si>
+  <si>
+    <t>Risk: first option</t>
+  </si>
+  <si>
+    <t>Employer, Risk (Critical / High / Moderate / Low / Unknown) and Account status (Active / Pending activation) filters are offered and applying one re-renders the list without an error.</t>
+  </si>
+  <si>
+    <t>AP_TC_288</t>
+  </si>
+  <si>
+    <t>Verify "Assign" opens the advisor-choice wizard with a confirmation step (cancelled before confirming)</t>
+  </si>
+  <si>
+    <t>At least one pending member exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Assign" on a pending member.
+2. Search and select an advisor.
+3. Click "Assign 1 member".
+4. Observe the confirmation; click Cancel.</t>
+  </si>
+  <si>
+    <t>Advisor: first advisor in the list</t>
+  </si>
+  <si>
+    <t>Step 2 of the wizard lists advisors with radio selection and filters; "Assign 1 member" is disabled until an advisor is chosen; clicking it asks "Assign this member?" with Cancel / Yes, assign.</t>
+  </si>
+  <si>
+    <t>AP_TC_289</t>
+  </si>
+  <si>
+    <t>Verify selecting members with the checkboxes switches to bulk assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tick the checkbox on a pending member row.
+2. Observe the per-row Assign action.</t>
+  </si>
+  <si>
+    <t>With rows selected, the per-row Assign buttons are disabled in favour of the bulk action, and "Select all on this page" is available.</t>
+  </si>
+  <si>
+    <t>AP_TC_290</t>
+  </si>
+  <si>
+    <t>Verify an assigned member's Actions menu offers View history and Reassign, and View history shows the assignment history</t>
+  </si>
+  <si>
+    <t>At least one assigned member exists.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the "Assigned" tab.
+2. Click "Actions for &lt;member&gt;".
+3. Click "View history".</t>
+  </si>
+  <si>
+    <t>First assigned member</t>
+  </si>
+  <si>
+    <t>The menu offers "View history" and "Reassign"; View history lists the current advisor (marked Current) and any previous advisors with their periods.</t>
+  </si>
+  <si>
+    <t>AP_TC_291</t>
+  </si>
+  <si>
+    <t>Verify a pending member can be assigned and then reassigned to another advisor (write path)</t>
+  </si>
+  <si>
+    <t>ADMIN_WRITE_TESTS=1; at least one pending member and two advisors exist. Leaves the member assigned to the second advisor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Assign the last pending member to the first advisor and confirm.
+2. On the Assigned tab, open Actions → Reassign for that member.
+3. Choose a different advisor, click "Reassign member" and confirm.</t>
+  </si>
+  <si>
+    <t>Member: last pending member; advisors: first two in the roster</t>
+  </si>
+  <si>
+    <t>After "Yes, assign" the member appears on the Assigned tab under the first advisor; after "Yes, reassign" the row shows the second advisor.</t>
+  </si>
+  <si>
+    <t>AP_TC_292</t>
+  </si>
+  <si>
+    <t>Verify the Departures status tabs filter the list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Admin → Departures.
+2. Click each tab in turn.</t>
+  </si>
+  <si>
+    <t>Tabs: All open, Not started, In progress, With Command Center, Closed, Departed</t>
+  </si>
+  <si>
+    <t>Each tab re-renders the list (rows or "No departures") without an error and the clicked tab is marked pressed.</t>
+  </si>
+  <si>
+    <t>AP_TC_293</t>
+  </si>
+  <si>
+    <t>Verify Assessment Audit search/filters work and "Export CSV" downloads a CSV file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Admin → Assessment Audit Log.
+2. Observe the time / advisor / member / assessment filters.
+3. Click "Export CSV".</t>
+  </si>
+  <si>
+    <t>The audit table (Member, Changes, Assessments, Advisor, Last activity) and filters load; Export CSV downloads a .csv whose header starts with "When","Action","Advisor".</t>
+  </si>
+  <si>
+    <t>AP_TC_294</t>
+  </si>
+  <si>
+    <t>Verify Follow-ups shows its figures and the flag / source / advisor filters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Admin → Follow-ups.
+2. Observe the stat tiles.
+3. Open the flag filter.</t>
+  </si>
+  <si>
+    <t>Never Scheduled, Dropped Off, Awaiting Confirmation and Overdue Sessions tiles are shown; the flag filter lists Booking blocked, Can't reach member, Didn't attend, Session overdue, Awaiting confirmation, Never scheduled and Dropped off; the list loads with a "Follow-ups (n)" count.</t>
+  </si>
+  <si>
+    <t>AP_TC_295</t>
+  </si>
+  <si>
+    <t>Verify the Advisor notifications console exposes engine/delivery controls and each notification tab; toggles require Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Admin → Notifications.
+2. Observe the Engine and Delivery switches, run/send times and channels.
+3. Toggle "Push channel" off and on again.
+4. Open each tab.</t>
+  </si>
+  <si>
+    <t>Engine enabled / run time / timezone, Delivery enabled / default send time, Push and Email channel switches are shown; a Save control appears for changes; the Sessions today, First session, Care backlog, Daily email, Follow-up 1, Follow-up 2 and Escalate to advisor tabs each open.</t>
+  </si>
+  <si>
+    <t>AP_TC_296</t>
+  </si>
+  <si>
+    <t>Verify the Administration sidebar links reach every admin page and "Back to main page" leaves the admin area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Admin.
+2. Click Overview, Advisors, Members, Follow-ups, Departures, Assessment Audit Log and Notifications in turn.
+3. Click "Back to main page".</t>
+  </si>
+  <si>
+    <t>Each link opens its admin page; Back to main page returns to the workspace.</t>
+  </si>
+  <si>
+    <t>AP_TC_153</t>
+  </si>
+  <si>
+    <t>Advisor Portal → Messages</t>
+  </si>
+  <si>
+    <t>Verify the Communication Center loads delivery stats, channel tabs and the member list</t>
+  </si>
+  <si>
+    <t>Advisor is logged in with at least one assigned member.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open Communication Center from the sidebar.
+2. Observe the stat tiles, channel tabs, search box and member list.</t>
+  </si>
+  <si>
+    <t>The Communication Center heading is shown with Emails Sent Today, SMS Sent Today, Delivered and Failed Deliveries tiles, the In-app chat / Email / SMS tabs, a member search box and at least one member entry.</t>
+  </si>
+  <si>
+    <t>AP_TC_154</t>
+  </si>
+  <si>
+    <t>Verify the Email and SMS channel tabs switch the member list and empty states</t>
+  </si>
+  <si>
+    <t>Advisor is on the Communication Center page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the "Email" tab and observe the list.
+2. Click the "SMS" tab and observe the list.
+3. Click "In-app chat" to return.</t>
+  </si>
+  <si>
+    <t>Channels: In-app chat, Email, SMS</t>
+  </si>
+  <si>
+    <t>Each tab re-renders the member list for that channel (e.g. "No email sent" / "No SMS sent" per member) and the thread pane shows the channel-specific empty state until a member is selected.</t>
+  </si>
+  <si>
+    <t>AP_TC_155</t>
+  </si>
+  <si>
+    <t>Verify selecting a member opens the in-app chat thread with a composer</t>
+  </si>
+  <si>
+    <t>Advisor is on the Communication Center page (In-app chat tab).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click a member in the list.
+2. Observe the thread pane and the member overview panel.</t>
+  </si>
+  <si>
+    <t>Member: Bruce Banner</t>
+  </si>
+  <si>
+    <t>The thread pane opens for that member with a "Message…" composer whose Send button is disabled while empty, and the right-hand panel shows the member's details (name, age, contact).</t>
+  </si>
+  <si>
+    <t>AP_TC_156</t>
+  </si>
+  <si>
+    <t>NEGATIVE - Verify searching members for an unknown name empties the member list</t>
+  </si>
+  <si>
+    <t>Advisor is on the Communication Center page with members listed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Type a name that cannot match into "Search members or messages…".
+2. Observe the member list.</t>
+  </si>
+  <si>
+    <t>Search term: "zzzzz-no-such-recipient"</t>
+  </si>
+  <si>
+    <t>No member entries remain in the list and the page does not error.</t>
+  </si>
+  <si>
+    <t>AP_TC_273</t>
+  </si>
+  <si>
+    <t>Verify the advisor can send an in-app chat message to a member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select a member in the In-app chat tab.
+2. Type a message in the composer.
+3. Click Send.</t>
+  </si>
+  <si>
+    <t>Member: Bruce Banner; Message: "Automated test message - please ignore."</t>
+  </si>
+  <si>
+    <t>Send becomes enabled once text is entered; after sending, the message appears in the thread.</t>
+  </si>
+  <si>
+    <t>AP_TC_274</t>
+  </si>
+  <si>
+    <t>Verify the advisor can send an Email to a member from the Email tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the "Email" tab and select a member.
+2. Enter a Subject and body.
+3. Click "Send email".</t>
+  </si>
+  <si>
+    <t>Member: Bruce Banner; Subject: "Automated test email"</t>
+  </si>
+  <si>
+    <t>"Send email" is disabled until subject and body are filled; after sending, the thread shows the email as sent.</t>
+  </si>
+  <si>
+    <t>AP_TC_275</t>
+  </si>
+  <si>
+    <t>Verify the advisor can send an SMS to a member from the SMS tab</t>
+  </si>
+  <si>
+    <t>Advisor is on the Communication Center page; member has a phone number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the "SMS" tab and select a member.
+2. Type the text.
+3. Click Send.</t>
+  </si>
+  <si>
+    <t>Member: Bruce Banner; Text: "Automated test SMS - please ignore."</t>
+  </si>
+  <si>
+    <t>The SMS composer sends the text and it appears in the thread with a delivery status.</t>
+  </si>
+  <si>
+    <t>AP_TC_276</t>
+  </si>
+  <si>
+    <t>Verify the member overview panel shows caseload and channel totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open the "SMS" tab.
+2. Observe the right-hand overview panel.</t>
+  </si>
+  <si>
+    <t>The panel shows "Members contacted", "SMS sent", "Failed" and a Caseload block with "Assigned members".</t>
+  </si>
+  <si>
+    <t>AP_TC_208</t>
+  </si>
+  <si>
+    <t>Verify each Dashboard stat tile drills down to its page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click Today's Sessions.
+2. Return; click Care Requests Pending.
+3. Return; click Total Members.
+4. Return; click Sessions Completed.</t>
+  </si>
+  <si>
+    <t>Today's Sessions and Sessions Completed open /wellness/sessions, Care Requests Pending opens /wellness/care-scheduler, Total Members opens /wellness/members.</t>
+  </si>
+  <si>
+    <t>AP_TC_209</t>
+  </si>
+  <si>
+    <t>Verify the Upcoming Sessions and Tasks &amp; Follow-ups "View all" links navigate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "View all" on Upcoming Sessions.
+2. Return; click "View all" on Tasks &amp; Follow-ups.</t>
+  </si>
+  <si>
+    <t>Upcoming Sessions opens /wellness/sessions and Tasks &amp; Follow-ups opens /wellness/care-scheduler.</t>
+  </si>
+  <si>
+    <t>AP_TC_210</t>
+  </si>
+  <si>
+    <t>Verify the Recent Members, Upcoming Sessions and Tasks &amp; Follow-ups panels render their content</t>
+  </si>
+  <si>
+    <t>Advisor is on the Dashboard with members and care requests.</t>
+  </si>
+  <si>
+    <t>1. Observe the three panels.</t>
+  </si>
+  <si>
+    <t>Recent Members shows "n of m · newest first" with member cards and join dates; Upcoming Sessions lists next sessions (or an empty state); Tasks &amp; Follow-ups lists open care requests with days open.</t>
+  </si>
+  <si>
+    <t>AP_TC_211</t>
+  </si>
+  <si>
+    <t>Verify the member status filter offers Active / Pending and filters the list</t>
+  </si>
+  <si>
+    <t>Advisor is on the Members page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open "Filter by status".
+2. Choose "Active".
+3. Observe the STATUS column.</t>
+  </si>
+  <si>
+    <t>Status: Active</t>
+  </si>
+  <si>
+    <t>All / Active / Pending are offered and every remaining row shows the chosen status.</t>
+  </si>
+  <si>
+    <t>AP_TC_212</t>
+  </si>
+  <si>
+    <t>Verify the employer filter narrows the list to one employer</t>
+  </si>
+  <si>
+    <t>Advisor is on the Members page with members from more than one employer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Filter by employer…" and pick an employer.
+2. Observe the EMPLOYER column.
+3. Click "Clear all".</t>
+  </si>
+  <si>
+    <t>First employer option</t>
+  </si>
+  <si>
+    <t>Every remaining row belongs to the chosen employer; Clear all restores the full list.</t>
+  </si>
+  <si>
+    <t>AP_TC_213</t>
+  </si>
+  <si>
+    <t>Verify clicking a column header sorts the list</t>
+  </si>
+  <si>
+    <t>Advisor is on the Members page with several members.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the first member.
+2. Click the "Member" column header twice.
+3. Compare the first member.</t>
+  </si>
+  <si>
+    <t>The order changes between ascending and descending.</t>
+  </si>
+  <si>
+    <t>AP_TC_214</t>
+  </si>
+  <si>
+    <t>Verify the Members stat tiles include Total, Completed Sessions, Pending Members and Upcoming Sessions</t>
+  </si>
+  <si>
+    <t>1. Observe the tiles.</t>
+  </si>
+  <si>
+    <t>Total Members, Completed Sessions, Pending Members and Upcoming Sessions tiles are shown with counts.</t>
+  </si>
+  <si>
+    <t>AP_TC_215</t>
+  </si>
+  <si>
+    <t>Verify Grid view shows one card per member with a View action</t>
+  </si>
+  <si>
+    <t>Advisor is on the Members page in List view.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Note the row count.
+2. Click "Grid".
+3. Count the View actions.</t>
+  </si>
+  <si>
+    <t>Grid view shows the same number of member cards (View actions) as the list had rows.</t>
+  </si>
+  <si>
+    <t>AP_TC_202</t>
+  </si>
+  <si>
+    <t>Verify "Sign out" ends the session and protected routes redirect to /login</t>
+  </si>
+  <si>
+    <t>Advisor is logged in. Runs last: it invalidates the saved session for this browser context only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Sign out" in the sidebar.
+2. Observe the page.
+3. Navigate to /wellness/dashboard.</t>
+  </si>
+  <si>
+    <t>The app returns to /login, the session token is cleared and the dashboard redirects to /login.</t>
+  </si>
+  <si>
     <t>Summary</t>
   </si>
   <si>
@@ -4389,40 +6144,31 @@
     <t>100%</t>
   </si>
   <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>1%</t>
+    <t>41%</t>
+  </si>
+  <si>
+    <t>0%</t>
   </si>
   <si>
     <t>Blocked</t>
   </si>
   <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>Not Executed</t>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>59%</t>
   </si>
   <si>
     <t>Automated</t>
   </si>
   <si>
-    <t>35%</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
-    <t>65%</t>
-  </si>
-  <si>
     <t>Suite result</t>
   </si>
   <si>
-    <t>FAILED</t>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>Cases</t>
@@ -4990,7 +6736,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I189"/>
+  <dimension ref="A1:I293"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -8546,10 +10292,10 @@
         <v>776</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -8575,10 +10321,10 @@
         <v>784</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -8586,115 +10332,115 @@
         <v>785</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>801</v>
+      </c>
+      <c r="F129" s="9" t="s">
         <v>796</v>
       </c>
-      <c r="B129" s="9" t="s">
-        <v>779</v>
-      </c>
-      <c r="C129" s="9" t="s">
-        <v>797</v>
-      </c>
-      <c r="D129" s="9" t="s">
-        <v>798</v>
-      </c>
-      <c r="E129" s="9" t="s">
-        <v>799</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>789</v>
-      </c>
       <c r="G129" s="9" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I129" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>807</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -8702,289 +10448,289 @@
         <v>808</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I131" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="F134" s="6" t="s">
         <v>825</v>
       </c>
-      <c r="B134" s="6" t="s">
-        <v>802</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>826</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>827</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>789</v>
-      </c>
       <c r="G134" s="6" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>831</v>
+        <v>809</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I135" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I137" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>849</v>
+        <v>796</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>857</v>
+        <v>333</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>858</v>
+        <v>777</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C140" s="6" t="s">
         <v>859</v>
       </c>
-      <c r="B140" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="C140" s="6" t="s">
+      <c r="D140" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="E140" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="E140" s="6" t="s">
+      <c r="F140" s="6" t="s">
         <v>862</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>789</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>863</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -8992,36 +10738,36 @@
         <v>864</v>
       </c>
       <c r="B141" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C141" s="9" t="s">
         <v>865</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="D141" s="9" t="s">
         <v>866</v>
       </c>
-      <c r="D141" s="9" t="s">
+      <c r="E141" s="9" t="s">
         <v>867</v>
       </c>
-      <c r="E141" s="9" t="s">
+      <c r="F141" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G141" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="F141" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G141" s="9" t="s">
-        <v>869</v>
-      </c>
       <c r="H141" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I141" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="B142" s="6" t="s">
         <v>870</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>865</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>871</v>
@@ -9033,45 +10779,45 @@
         <v>873</v>
       </c>
       <c r="F142" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G142" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="G142" s="6" t="s">
-        <v>875</v>
-      </c>
       <c r="H142" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C143" s="9" t="s">
         <v>876</v>
       </c>
-      <c r="B143" s="9" t="s">
-        <v>865</v>
-      </c>
-      <c r="C143" s="9" t="s">
+      <c r="D143" s="9" t="s">
         <v>877</v>
       </c>
-      <c r="D143" s="9" t="s">
+      <c r="E143" s="9" t="s">
         <v>878</v>
       </c>
-      <c r="E143" s="9" t="s">
+      <c r="F143" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="F143" s="9" t="s">
-        <v>818</v>
       </c>
       <c r="G143" s="9" t="s">
         <v>880</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -9079,28 +10825,28 @@
         <v>881</v>
       </c>
       <c r="B144" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="D144" s="6" t="s">
         <v>883</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>833</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>884</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>789</v>
+        <v>825</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>885</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -9108,71 +10854,71 @@
         <v>886</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>888</v>
+        <v>840</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>889</v>
       </c>
       <c r="F145" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G145" s="9" t="s">
         <v>890</v>
       </c>
-      <c r="G145" s="9" t="s">
-        <v>891</v>
-      </c>
       <c r="H145" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I145" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>892</v>
       </c>
-      <c r="B146" s="6" t="s">
-        <v>882</v>
-      </c>
-      <c r="C146" s="6" t="s">
+      <c r="D146" s="6" t="s">
         <v>893</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="E146" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="E146" s="6" t="s">
+      <c r="F146" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="G146" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="G146" s="6" t="s">
-        <v>897</v>
-      </c>
       <c r="H146" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="C147" s="9" t="s">
         <v>898</v>
       </c>
-      <c r="B147" s="9" t="s">
-        <v>882</v>
-      </c>
-      <c r="C147" s="9" t="s">
+      <c r="D147" s="9" t="s">
         <v>899</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>894</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>900</v>
@@ -9184,10 +10930,10 @@
         <v>902</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I147" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -9195,13 +10941,13 @@
         <v>903</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>904</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>905</v>
@@ -9213,10 +10959,10 @@
         <v>907</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -9224,86 +10970,86 @@
         <v>908</v>
       </c>
       <c r="B149" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="C149" s="9" t="s">
         <v>909</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="D149" s="9" t="s">
+        <v>899</v>
+      </c>
+      <c r="E149" s="9" t="s">
         <v>910</v>
       </c>
-      <c r="D149" s="9" t="s">
+      <c r="F149" s="9" t="s">
         <v>911</v>
       </c>
-      <c r="E149" s="9" t="s">
+      <c r="G149" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="F149" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G149" s="9" t="s">
-        <v>913</v>
-      </c>
       <c r="H149" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="C150" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="B150" s="6" t="s">
-        <v>909</v>
-      </c>
-      <c r="C150" s="6" t="s">
+      <c r="D150" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="E150" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E150" s="6" t="s">
+      <c r="F150" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="F150" s="6" t="s">
+      <c r="G150" s="6" t="s">
         <v>918</v>
       </c>
-      <c r="G150" s="6" t="s">
-        <v>919</v>
-      </c>
       <c r="H150" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="C151" s="9" t="s">
         <v>920</v>
       </c>
-      <c r="B151" s="9" t="s">
-        <v>909</v>
-      </c>
-      <c r="C151" s="9" t="s">
+      <c r="D151" s="9" t="s">
         <v>921</v>
       </c>
-      <c r="D151" s="9" t="s">
+      <c r="E151" s="9" t="s">
         <v>922</v>
       </c>
-      <c r="E151" s="9" t="s">
+      <c r="F151" s="9" t="s">
         <v>923</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>789</v>
       </c>
       <c r="G151" s="9" t="s">
         <v>924</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -9311,13 +11057,13 @@
         <v>925</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>909</v>
+        <v>887</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>926</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>916</v>
+        <v>921</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>927</v>
@@ -9329,10 +11075,10 @@
         <v>929</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
@@ -9340,28 +11086,28 @@
         <v>930</v>
       </c>
       <c r="B153" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="C153" s="9" t="s">
         <v>931</v>
       </c>
-      <c r="C153" s="9" t="s">
+      <c r="D153" s="9" t="s">
         <v>932</v>
-      </c>
-      <c r="D153" s="9" t="s">
-        <v>833</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>933</v>
       </c>
       <c r="F153" s="9" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G153" s="9" t="s">
         <v>934</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -9369,1043 +11115,4059 @@
         <v>935</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>931</v>
+        <v>887</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>936</v>
       </c>
       <c r="D154" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="E154" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="E154" s="6" t="s">
+      <c r="F154" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G154" s="6" t="s">
         <v>938</v>
       </c>
-      <c r="F154" s="6" t="s">
-        <v>939</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>940</v>
-      </c>
       <c r="H154" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="C155" s="9" t="s">
         <v>941</v>
       </c>
-      <c r="B155" s="9" t="s">
-        <v>931</v>
-      </c>
-      <c r="C155" s="9" t="s">
+      <c r="D155" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="E155" s="9" t="s">
         <v>942</v>
       </c>
-      <c r="D155" s="9" t="s">
+      <c r="F155" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G155" s="9" t="s">
         <v>943</v>
       </c>
-      <c r="E155" s="9" t="s">
-        <v>944</v>
-      </c>
-      <c r="F155" s="9" t="s">
-        <v>945</v>
-      </c>
-      <c r="G155" s="9" t="s">
-        <v>946</v>
-      </c>
       <c r="H155" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I155" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="E156" s="6" t="s">
         <v>947</v>
       </c>
-      <c r="B156" s="6" t="s">
-        <v>931</v>
-      </c>
-      <c r="C156" s="6" t="s">
+      <c r="F156" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G156" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="D156" s="6" t="s">
-        <v>949</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>950</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>951</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>952</v>
-      </c>
       <c r="H156" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>950</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>951</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="F157" s="9" t="s">
         <v>953</v>
       </c>
-      <c r="B157" s="9" t="s">
+      <c r="G157" s="9" t="s">
         <v>954</v>
       </c>
-      <c r="C157" s="9" t="s">
-        <v>955</v>
-      </c>
-      <c r="D157" s="9" t="s">
-        <v>833</v>
-      </c>
-      <c r="E157" s="9" t="s">
-        <v>956</v>
-      </c>
-      <c r="F157" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G157" s="9" t="s">
-        <v>957</v>
-      </c>
       <c r="H157" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I157" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="E158" s="6" t="s">
         <v>958</v>
       </c>
-      <c r="B158" s="6" t="s">
-        <v>954</v>
-      </c>
-      <c r="C158" s="6" t="s">
+      <c r="F158" s="6" t="s">
         <v>959</v>
       </c>
-      <c r="D158" s="6" t="s">
+      <c r="G158" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="E158" s="6" t="s">
-        <v>961</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>962</v>
-      </c>
-      <c r="G158" s="6" t="s">
-        <v>963</v>
-      </c>
       <c r="H158" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="C159" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>963</v>
+      </c>
+      <c r="E159" s="9" t="s">
         <v>964</v>
       </c>
-      <c r="B159" s="9" t="s">
-        <v>954</v>
-      </c>
-      <c r="C159" s="9" t="s">
+      <c r="F159" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G159" s="9" t="s">
         <v>965</v>
       </c>
-      <c r="D159" s="9" t="s">
-        <v>966</v>
-      </c>
-      <c r="E159" s="9" t="s">
-        <v>967</v>
-      </c>
-      <c r="F159" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G159" s="9" t="s">
-        <v>968</v>
-      </c>
       <c r="H159" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="s">
+        <v>966</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>968</v>
+      </c>
+      <c r="F160" s="6" t="s">
         <v>969</v>
       </c>
-      <c r="B160" s="6" t="s">
+      <c r="G160" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>971</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>972</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>973</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>974</v>
-      </c>
       <c r="H160" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>974</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G161" s="9" t="s">
         <v>975</v>
       </c>
-      <c r="B161" s="9" t="s">
-        <v>970</v>
-      </c>
-      <c r="C161" s="9" t="s">
-        <v>976</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>977</v>
-      </c>
-      <c r="E161" s="9" t="s">
-        <v>978</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G161" s="9" t="s">
-        <v>979</v>
-      </c>
       <c r="H161" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I161" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>979</v>
+      </c>
+      <c r="F162" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="G162" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="C162" s="6" t="s">
-        <v>982</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>983</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>984</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>985</v>
-      </c>
-      <c r="G162" s="6" t="s">
-        <v>986</v>
-      </c>
       <c r="H162" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="F163" s="9" t="s">
-        <v>991</v>
+        <v>796</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I163" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>989</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="F165" s="9" t="s">
-        <v>1002</v>
+        <v>796</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I165" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>1005</v>
+        <v>972</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>833</v>
+        <v>984</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>1009</v>
+        <v>333</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>280</v>
+        <v>777</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>1005</v>
+        <v>972</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>1012</v>
+        <v>984</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="F167" s="9" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G167" s="9" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I167" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>833</v>
+        <v>1013</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="F169" s="9" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I169" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>865</v>
+        <v>1017</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>789</v>
+        <v>1021</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>865</v>
+        <v>1017</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="D171" s="9" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E171" s="9" t="s">
         <v>1026</v>
       </c>
-      <c r="E171" s="9" t="s">
-        <v>1031</v>
-      </c>
       <c r="F171" s="9" t="s">
-        <v>789</v>
+        <v>1027</v>
       </c>
       <c r="G171" s="9" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I171" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G172" s="6" t="s">
         <v>1033</v>
       </c>
-      <c r="B172" s="6" t="s">
-        <v>970</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D172" s="6" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E172" s="6" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F172" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="G172" s="6" t="s">
-        <v>1037</v>
-      </c>
       <c r="H172" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F173" s="9" t="s">
         <v>1038</v>
       </c>
-      <c r="B173" s="9" t="s">
-        <v>970</v>
-      </c>
-      <c r="C173" s="9" t="s">
+      <c r="G173" s="9" t="s">
         <v>1039</v>
       </c>
-      <c r="D173" s="9" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E173" s="9" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F173" s="9" t="s">
-        <v>1042</v>
-      </c>
-      <c r="G173" s="9" t="s">
-        <v>1043</v>
-      </c>
       <c r="H173" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I173" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G174" s="6" t="s">
         <v>1044</v>
       </c>
-      <c r="B174" s="6" t="s">
-        <v>970</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D174" s="6" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E174" s="6" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F174" s="6" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G174" s="6" t="s">
-        <v>1048</v>
-      </c>
       <c r="H174" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F175" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G175" s="9" t="s">
         <v>1049</v>
       </c>
-      <c r="B175" s="9" t="s">
-        <v>970</v>
-      </c>
-      <c r="C175" s="9" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D175" s="9" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E175" s="9" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F175" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>1052</v>
-      </c>
       <c r="H175" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I175" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G176" s="6" t="s">
         <v>1053</v>
       </c>
-      <c r="B176" s="6" t="s">
-        <v>970</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E176" s="6" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F176" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="G176" s="6" t="s">
-        <v>1057</v>
-      </c>
       <c r="H176" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F177" s="9" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G177" s="9" t="s">
         <v>1058</v>
       </c>
-      <c r="B177" s="9" t="s">
-        <v>970</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D177" s="9" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E177" s="9" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F177" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G177" s="9" t="s">
-        <v>1061</v>
-      </c>
       <c r="H177" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I177" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F178" s="6" t="s">
         <v>1062</v>
       </c>
-      <c r="B178" s="6" t="s">
-        <v>970</v>
-      </c>
-      <c r="C178" s="6" t="s">
+      <c r="G178" s="6" t="s">
         <v>1063</v>
       </c>
-      <c r="D178" s="6" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E178" s="6" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F178" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="G178" s="6" t="s">
-        <v>1065</v>
-      </c>
       <c r="H178" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E179" s="9" t="s">
         <v>1066</v>
       </c>
-      <c r="B179" s="9" t="s">
-        <v>970</v>
-      </c>
-      <c r="C179" s="9" t="s">
+      <c r="F179" s="9" t="s">
         <v>1067</v>
       </c>
-      <c r="D179" s="9" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E179" s="9" t="s">
+      <c r="G179" s="9" t="s">
         <v>1068</v>
       </c>
-      <c r="F179" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G179" s="9" t="s">
-        <v>1069</v>
-      </c>
       <c r="H179" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I179" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C180" s="6" t="s">
         <v>1070</v>
       </c>
-      <c r="B180" s="6" t="s">
-        <v>970</v>
-      </c>
-      <c r="C180" s="6" t="s">
+      <c r="D180" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E180" s="6" t="s">
         <v>1071</v>
       </c>
-      <c r="D180" s="6" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E180" s="6" t="s">
+      <c r="F180" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G180" s="6" t="s">
         <v>1072</v>
       </c>
-      <c r="F180" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="G180" s="6" t="s">
-        <v>1073</v>
-      </c>
       <c r="H180" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C181" s="9" t="s">
         <v>1074</v>
       </c>
-      <c r="B181" s="9" t="s">
+      <c r="D181" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E181" s="9" t="s">
         <v>1075</v>
       </c>
-      <c r="C181" s="9" t="s">
+      <c r="F181" s="9" t="s">
         <v>1076</v>
       </c>
-      <c r="D181" s="9" t="s">
+      <c r="G181" s="9" t="s">
         <v>1077</v>
       </c>
-      <c r="E181" s="9" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F181" s="9" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G181" s="9" t="s">
-        <v>1079</v>
-      </c>
       <c r="H181" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I181" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E182" s="6" t="s">
         <v>1080</v>
       </c>
-      <c r="B182" s="6" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C182" s="6" t="s">
+      <c r="F182" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G182" s="6" t="s">
         <v>1081</v>
       </c>
-      <c r="D182" s="6" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E182" s="6" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F182" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="G182" s="6" t="s">
-        <v>1084</v>
-      </c>
       <c r="H182" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="E183" s="9" t="s">
         <v>1085</v>
       </c>
-      <c r="B183" s="9" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C183" s="9" t="s">
+      <c r="F183" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G183" s="9" t="s">
         <v>1086</v>
       </c>
-      <c r="D183" s="9" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E183" s="9" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F183" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="G183" s="9" t="s">
-        <v>1088</v>
-      </c>
       <c r="H183" s="9" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I183" s="10" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D184" s="6" t="s">
         <v>1089</v>
       </c>
-      <c r="B184" s="6" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C184" s="6" t="s">
+      <c r="E184" s="6" t="s">
         <v>1090</v>
       </c>
-      <c r="D184" s="6" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E184" s="6" t="s">
+      <c r="F184" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G184" s="6" t="s">
         <v>1091</v>
       </c>
-      <c r="F184" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="G184" s="6" t="s">
-        <v>1092</v>
-      </c>
       <c r="H184" s="6" t="s">
-        <v>777</v>
+        <v>333</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>20</v>
+        <v>777</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C185" s="9" t="s">
         <v>1093</v>
       </c>
-      <c r="B185" s="9" t="s">
+      <c r="D185" s="9" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E185" s="9" t="s">
         <v>1094</v>
       </c>
-      <c r="C185" s="9" t="s">
+      <c r="F185" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G185" s="9" t="s">
         <v>1095</v>
       </c>
-      <c r="D185" s="9" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E185" s="9" t="s">
-        <v>1097</v>
-      </c>
-      <c r="F185" s="9" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G185" s="9" t="s">
-        <v>1099</v>
-      </c>
       <c r="H185" s="9" t="s">
-        <v>857</v>
+        <v>333</v>
       </c>
       <c r="I185" s="10" t="s">
-        <v>858</v>
+        <v>777</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G186" s="6" t="s">
         <v>1100</v>
       </c>
-      <c r="B186" s="6" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C186" s="6" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D186" s="6" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E186" s="6" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F186" s="6" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G186" s="6" t="s">
-        <v>1105</v>
-      </c>
       <c r="H186" s="6" t="s">
-        <v>857</v>
+        <v>333</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>858</v>
+        <v>777</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G187" s="9" t="s">
         <v>1106</v>
       </c>
-      <c r="B187" s="9" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C187" s="9" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D187" s="9" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E187" s="9" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F187" s="9" t="s">
-        <v>1110</v>
-      </c>
-      <c r="G187" s="9" t="s">
-        <v>1111</v>
-      </c>
       <c r="H187" s="9" t="s">
-        <v>857</v>
+        <v>333</v>
       </c>
       <c r="I187" s="10" t="s">
-        <v>858</v>
+        <v>777</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>1094</v>
+        <v>1006</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>1114</v>
+        <v>1103</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>857</v>
+        <v>333</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>858</v>
+        <v>777</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F189" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H189" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I189" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D190" s="6" t="s">
         <v>1118</v>
       </c>
-      <c r="B189" s="9" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C189" s="9" t="s">
+      <c r="E190" s="6" t="s">
         <v>1119</v>
       </c>
-      <c r="D189" s="9" t="s">
+      <c r="F190" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="G190" s="6" t="s">
         <v>1120</v>
       </c>
-      <c r="E189" s="9" t="s">
+      <c r="H190" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="8" t="s">
         <v>1121</v>
       </c>
-      <c r="F189" s="9" t="s">
+      <c r="B191" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C191" s="9" t="s">
         <v>1122</v>
       </c>
-      <c r="G189" s="9" t="s">
+      <c r="D191" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E191" s="9" t="s">
         <v>1123</v>
       </c>
-      <c r="H189" s="9" t="s">
-        <v>857</v>
-      </c>
-      <c r="I189" s="10" t="s">
-        <v>858</v>
+      <c r="F191" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H191" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I191" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="8" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H193" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I193" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G194" s="6" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="8" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H195" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I195" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G196" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H196" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="8" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H197" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I197" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G198" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H198" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="8" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H199" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I199" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F200" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G200" s="6" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H200" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="8" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H201" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I201" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G202" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H202" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H203" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I203" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F204" s="6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G204" s="6" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H204" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="8" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H205" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I205" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G206" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H206" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="8" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H207" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I207" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F208" s="6" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G208" s="6" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H208" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="8" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D209" s="9" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H209" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I209" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F210" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G210" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H210" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="8" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="E211" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H211" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I211" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G212" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H212" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I212" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D213" s="9" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E213" s="9" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F213" s="9" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G213" s="9" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H213" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I213" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G214" s="6" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H214" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I214" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F215" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H215" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I215" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G216" s="6" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H216" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C217" s="9" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F217" s="9" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H217" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I217" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G218" s="6" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H218" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I218" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B219" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E219" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F219" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H219" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I219" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G220" s="6" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H220" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="8" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D221" s="9" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E221" s="9" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F221" s="9" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G221" s="9" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H221" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I221" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>1285</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G222" s="6" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H222" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I222" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F223" s="9" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H223" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I223" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G224" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H224" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I224" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="8" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F225" s="9" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>1301</v>
+      </c>
+      <c r="H225" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I225" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G226" s="6" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H226" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I226" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="8" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C227" s="9" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F227" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H227" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I227" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G228" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="H228" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I228" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="8" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F229" s="9" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H229" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I229" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E230" s="6" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F230" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G230" s="6" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H230" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I230" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C231" s="9" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F231" s="9" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H231" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I231" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G232" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H232" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I232" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="8" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H233" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I233" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F234" s="6" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G234" s="6" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H234" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I234" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="8" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C235" s="9" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F235" s="9" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G235" s="9" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H235" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I235" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F236" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G236" s="6" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H236" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I236" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="8" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C237" s="9" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D237" s="9" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F237" s="9" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H237" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I237" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F238" s="6" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G238" s="6" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H238" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I238" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C239" s="9" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F239" s="9" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>1375</v>
+      </c>
+      <c r="H239" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I239" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F240" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G240" s="6" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H240" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I240" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="8" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F241" s="9" t="s">
+        <v>1385</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H241" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I241" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F242" s="6" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G242" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H242" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I242" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="8" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F243" s="9" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G243" s="9" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H243" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I243" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D244" s="6" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F244" s="6" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G244" s="6" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H244" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I244" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="8" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D245" s="9" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F245" s="9" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G245" s="9" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H245" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I245" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F246" s="6" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G246" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H246" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I246" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F247" s="9" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G247" s="9" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H247" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I247" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="5" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G248" s="6" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H248" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I248" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D249" s="9" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F249" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G249" s="9" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H249" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I249" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="5" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E250" s="6" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F250" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G250" s="6" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H250" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I250" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="8" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F251" s="9" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G251" s="9" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H251" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I251" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="5" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F252" s="6" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G252" s="6" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H252" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I252" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D253" s="9" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E253" s="9" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F253" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G253" s="9" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H253" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I253" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="5" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F254" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G254" s="6" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H254" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I254" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="E255" s="9" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F255" s="9" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G255" s="9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H255" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I255" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="5" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F256" s="6" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G256" s="6" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H256" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="8" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D257" s="9" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E257" s="9" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F257" s="9" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G257" s="9" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H257" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I257" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F258" s="6" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G258" s="6" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H258" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I258" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="8" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F259" s="9" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G259" s="9" t="s">
+        <v>1482</v>
+      </c>
+      <c r="H259" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I259" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="5" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D260" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F260" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G260" s="6" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H260" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="8" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D261" s="9" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E261" s="9" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F261" s="9" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G261" s="9" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H261" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I261" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="5" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F262" s="6" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G262" s="6" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H262" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I262" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="8" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D263" s="9" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E263" s="9" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F263" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G263" s="9" t="s">
+        <v>1502</v>
+      </c>
+      <c r="H263" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I263" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="5" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D264" s="6" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F264" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G264" s="6" t="s">
+        <v>1507</v>
+      </c>
+      <c r="H264" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I264" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="8" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F265" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G265" s="9" t="s">
+        <v>1511</v>
+      </c>
+      <c r="H265" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I265" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="5" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F266" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G266" s="6" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H266" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I266" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="8" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D267" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E267" s="9" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F267" s="9" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G267" s="9" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H267" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I267" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="5" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F268" s="6" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G268" s="6" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H268" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I268" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="8" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E269" s="9" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F269" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G269" s="9" t="s">
+        <v>1530</v>
+      </c>
+      <c r="H269" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I269" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="5" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E270" s="6" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F270" s="6" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G270" s="6" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H270" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I270" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="8" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E271" s="9" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F271" s="9" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H271" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I271" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="5" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F272" s="6" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G272" s="6" t="s">
+        <v>1547</v>
+      </c>
+      <c r="H272" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="8" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B273" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D273" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E273" s="9" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F273" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G273" s="9" t="s">
+        <v>1551</v>
+      </c>
+      <c r="H273" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I273" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="5" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D274" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F274" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G274" s="6" t="s">
+        <v>1555</v>
+      </c>
+      <c r="H274" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I274" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="8" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E275" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F275" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G275" s="9" t="s">
+        <v>1559</v>
+      </c>
+      <c r="H275" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I275" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F276" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G276" s="6" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H276" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I276" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="8" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B277" s="9" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D277" s="9" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E277" s="9" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F277" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G277" s="9" t="s">
+        <v>1569</v>
+      </c>
+      <c r="H277" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I277" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F278" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G278" s="6" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H278" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I278" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="8" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B279" s="9" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D279" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E279" s="9" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F279" s="9" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G279" s="9" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H279" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I279" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F280" s="6" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G280" s="6" t="s">
+        <v>1587</v>
+      </c>
+      <c r="H280" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I280" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="8" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B281" s="9" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D281" s="9" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E281" s="9" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F281" s="9" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G281" s="9" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H281" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I281" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="5" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F282" s="6" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G282" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="H282" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I282" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="8" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D283" s="9" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E283" s="9" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F283" s="9" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G283" s="9" t="s">
+        <v>1603</v>
+      </c>
+      <c r="H283" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I283" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F284" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G284" s="6" t="s">
+        <v>1607</v>
+      </c>
+      <c r="H284" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I284" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="8" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D285" s="9" t="s">
+        <v>805</v>
+      </c>
+      <c r="E285" s="9" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F285" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G285" s="9" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H285" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I285" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="5" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F286" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G286" s="6" t="s">
+        <v>1615</v>
+      </c>
+      <c r="H286" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I286" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="8" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B287" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>1617</v>
+      </c>
+      <c r="D287" s="9" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E287" s="9" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F287" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G287" s="9" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H287" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I287" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="5" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F288" s="6" t="s">
+        <v>1625</v>
+      </c>
+      <c r="G288" s="6" t="s">
+        <v>1626</v>
+      </c>
+      <c r="H288" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I288" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="8" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B289" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D289" s="9" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E289" s="9" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F289" s="9" t="s">
+        <v>1631</v>
+      </c>
+      <c r="G289" s="9" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H289" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I289" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="5" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F290" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G290" s="6" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H290" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I290" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="8" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B291" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D291" s="9" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E291" s="9" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F291" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G291" s="9" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H291" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I291" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="5" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F292" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="G292" s="6" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H292" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="8" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B293" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D293" s="9" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E293" s="9" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F293" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="G293" s="9" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H293" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I293" s="10" t="s">
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -10415,7 +15177,7 @@
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
-  <conditionalFormatting sqref="I6:I189">
+  <conditionalFormatting sqref="I6:I293">
     <cfRule type="containsText" dxfId="0" priority="1">
       <formula>NOT(ISERROR(SEARCH("Pass",I6)))</formula>
     </cfRule>
@@ -10433,10 +15195,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, Not Executed" sqref="I10:I189">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, Not Executed" sqref="I10:I293">
       <formula1>"Pass,Fail,Blocked,Skipped,Not Executed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, Not Executed" sqref="I6:I189">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid status" error="Pick one of: Pass, Fail, Blocked, Skipped, Not Executed" sqref="I6:I293">
       <formula1>"Pass,Fail,Blocked,Skipped,Not Executed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10447,7 +15209,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -10457,20 +15219,20 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>1124</v>
+        <v>1652</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
     <row r="3" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>1125</v>
+        <v>1653</v>
       </c>
       <c r="B3" s="13">
-        <v>184</v>
+        <v>288</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1126</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10478,10 +15240,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="15">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1127</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10489,73 +15251,73 @@
         <v>280</v>
       </c>
       <c r="B5" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1128</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>1129</v>
+        <v>1657</v>
       </c>
       <c r="B6" s="15">
         <v>0</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1130</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>858</v>
+        <v>1658</v>
       </c>
       <c r="B7" s="15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1131</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>1132</v>
+        <v>777</v>
       </c>
       <c r="B8" s="15">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>1130</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>1133</v>
+        <v>1660</v>
       </c>
       <c r="B10" s="13">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1134</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1135</v>
+        <v>1661</v>
       </c>
       <c r="B11" s="15">
         <v>119</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1136</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>1137</v>
+        <v>1662</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1138</v>
+        <v>1663</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>333</v>
@@ -10566,10 +15328,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>1139</v>
+        <v>1664</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1133</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -10585,153 +15347,153 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>970</v>
+        <v>1006</v>
       </c>
       <c r="B17" s="15">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C17" s="15">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>55</v>
+      <c r="A18" t="s">
+        <v>838</v>
       </c>
       <c r="B18" s="15">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C18" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>716</v>
+        <v>870</v>
       </c>
       <c r="B19" s="15">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C19" s="15">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>337</v>
+        <v>1238</v>
       </c>
       <c r="B20" s="15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C20" s="15">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B21" s="15">
         <v>13</v>
       </c>
-      <c r="B21" s="15">
-        <v>6</v>
-      </c>
       <c r="C21" s="15">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>210</v>
+        <v>809</v>
       </c>
       <c r="B22" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C22" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>831</v>
+        <v>887</v>
       </c>
       <c r="B23" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C23" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>1188</v>
       </c>
       <c r="B24" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C24" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="15">
+        <v>9</v>
+      </c>
+      <c r="C25" s="15">
         <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>802</v>
-      </c>
-      <c r="B25" s="15">
-        <v>5</v>
-      </c>
-      <c r="C25" s="15">
-        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>865</v>
+        <v>716</v>
       </c>
       <c r="B26" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>882</v>
+        <v>1041</v>
       </c>
       <c r="B27" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C27" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>1094</v>
+        <v>1138</v>
       </c>
       <c r="B28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>282</v>
+        <v>1565</v>
       </c>
       <c r="B29" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C29" s="15">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="B30" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C30" s="15">
         <v>0</v>
@@ -10739,65 +15501,65 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="B31" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C31" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>909</v>
+        <v>972</v>
       </c>
       <c r="B32" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C32" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>931</v>
+        <v>13</v>
       </c>
       <c r="B33" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C33" s="15">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>981</v>
+        <v>210</v>
       </c>
       <c r="B34" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" s="15">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>1075</v>
+        <v>940</v>
       </c>
       <c r="B35" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="B36" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36" s="15">
         <v>0</v>
@@ -10805,10 +15567,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>224</v>
+        <v>282</v>
       </c>
       <c r="B37" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" s="15">
         <v>0</v>
@@ -10816,32 +15578,32 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>954</v>
+        <v>311</v>
       </c>
       <c r="B38" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>1005</v>
+      <c r="A39" t="s">
+        <v>1017</v>
       </c>
       <c r="B39" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="B40" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="15">
         <v>0</v>
@@ -10849,10 +15611,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="B41" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41" s="15">
         <v>0</v>
@@ -10860,7 +15622,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
       <c r="B42" s="15">
         <v>1</v>
@@ -10871,7 +15633,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B43" s="15">
         <v>1</v>
@@ -10882,7 +15644,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="B44" s="15">
         <v>1</v>
@@ -10893,7 +15655,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="B45" s="15">
         <v>1</v>
@@ -10904,7 +15666,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>386</v>
+        <v>172</v>
       </c>
       <c r="B46" s="15">
         <v>1</v>
@@ -10915,7 +15677,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>394</v>
+        <v>180</v>
       </c>
       <c r="B47" s="15">
         <v>1</v>
@@ -10926,7 +15688,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="B48" s="15">
         <v>1</v>
@@ -10937,7 +15699,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="B49" s="15">
         <v>1</v>
@@ -10948,7 +15710,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B50" s="15">
         <v>1</v>
@@ -10959,7 +15721,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B51" s="15">
         <v>1</v>
@@ -10970,23 +15732,56 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>771</v>
+        <v>415</v>
       </c>
       <c r="B52" s="15">
         <v>1</v>
       </c>
       <c r="C52" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1020</v>
+        <v>422</v>
       </c>
       <c r="B53" s="15">
         <v>1</v>
       </c>
       <c r="C53" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>771</v>
+      </c>
+      <c r="B54" s="15">
+        <v>1</v>
+      </c>
+      <c r="C54" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>779</v>
+      </c>
+      <c r="B55" s="15">
+        <v>1</v>
+      </c>
+      <c r="C55" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B56" s="15">
+        <v>1</v>
+      </c>
+      <c r="C56" s="15">
         <v>1</v>
       </c>
     </row>
